--- a/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
+++ b/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
@@ -23,7 +23,7 @@
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Comms!$A$4:$E$17</definedName>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'HubSpot Build Spec'!$A$4:$C$23</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Intake Form'!$A$4:$G$29</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'Open Questions'!$A$4:$E$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'Open Questions'!$A$4:$E$14</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Task Template'!$A$6:$L$83</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Tech Setup'!$A$4:$F$44</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Training!$A$4:$F$13</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="885">
   <si>
     <t xml:space="preserve">RevGravy · Marketing Hub Onboarding Process (draft v1)</t>
   </si>
@@ -2621,12 +2621,6 @@
   </si>
   <si>
     <t xml:space="preserve">Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is the Marketing Hub onboarding a fixed 90-day program? The roadmap assumes 90 days because of the '30 days before we finish' step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day offsets, MBR count, 'what's next' timing</t>
   </si>
   <si>
     <t xml:space="preserve">Which Marketing Hub tiers do we sell onboarding for (Starter, Pro, Enterprise)? Is there one package or several?</t>
@@ -3523,7 +3517,7 @@
     <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3575,18 +3569,18 @@
       </c>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E6" s="22"/>
     </row>
@@ -3595,7 +3589,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>866</v>
@@ -3610,22 +3604,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E8" s="22"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>871</v>
@@ -3640,7 +3634,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>873</v>
@@ -3655,22 +3649,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E11" s="22"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>878</v>
@@ -3680,12 +3674,12 @@
       </c>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>880</v>
@@ -3695,38 +3689,23 @@
       </c>
       <c r="E13" s="22"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>885</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="E15" s="22"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E15"/>
+  <autoFilter ref="A4:E14"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
+++ b/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1031">
   <si>
     <t xml:space="preserve">RevGravy · Marketing Hub Onboarding Process (v2)</t>
   </si>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">HubSpot Work Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">What to build in HubSpot Work: project fields, task columns, board, views, requests, portfolio, agents.</t>
+    <t xml:space="preserve">What to build in HubSpot Work: new-customer steps, task columns, board, views, requests, Customers table, agents.</t>
   </si>
   <si>
     <t xml:space="preserve">Tool Fit</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">Phil decides, based on capacity.</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio table has a capacity view (active customers per Architect).</t>
+    <t xml:space="preserve">Capacity report in the Onboarding Portfolio (active customers per Architect).</t>
   </si>
   <si>
     <t xml:space="preserve">HubSpot Work beta</t>
@@ -310,7 +310,16 @@
     <t xml:space="preserve">HubSpot Work can build agents.</t>
   </si>
   <si>
-    <t xml:space="preserve">8 agents added to the prompt. They only draft, fill dates or flag; none sends anything to a customer.</t>
+    <t xml:space="preserve">8 agents added. They only draft, fill dates or flag; none sends anything to a customer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HubSpot Work limits (found in the build)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No custom project fields; no links between tables and projects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer details live on the Customers table, matched to the project by its exact name. Due date uses two helper columns that the Date Setter agent fills.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope limits for migration and website work (suggested)</t>
@@ -748,10 +757,10 @@
     <t xml:space="preserve">Pick the Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Phil checks the capacity view (active customers per Architect) and picks the Architect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work: Portfolio (capacity view)</t>
+    <t xml:space="preserve">Phil checks the Capacity report (active customers per Architect) and picks the Architect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work: Capacity report</t>
   </si>
   <si>
     <t xml:space="preserve">1.02</t>
@@ -760,57 +769,60 @@
     <t xml:space="preserve">Create the customer project</t>
   </si>
   <si>
-    <t xml:space="preserve">Duplicate the 'Marketing Hub Onboarding (Template)' project, rename it '&lt;Client&gt; · Marketing Hub Onboarding', fill Company, Deal, Architect, Start date and Program length, and add a Portfolio row.</t>
+    <t xml:space="preserve">Duplicate the 'Marketing Hub Onboarding (Template)' project and name it exactly '&lt;Client&gt; · Marketing Hub Onboarding'. Add a Customers row with that exact name plus Company, Deal, Architect, Program length and Start date. Share the project with the Architect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work: customer project + Customers row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome email #1: welcome + Action Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent from Phil on Day 0: Supered Action Plan link, kickoff booking link, first to-dos (grant HubSpot access, fill the intake form).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HubSpot email (automated on deal stage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the Supered Action Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate the Marketing Hub Action Plan template; add the agreement, FigJam, client to-dos and access checklist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phil ↔ Architect handoff (30 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk through FigJam, customer context, products, the From→To goal, progress measures and KPIs, schedule. Architect checks the Handoff checklist section. Strategy lead moves to the Architect after this call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting on the deal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set up progress measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the customer's progress measures to the project (name '&lt;Client&gt; 1.1 Visitor to Lead' etc.) with baseline, target and schedule.</t>
   </si>
   <si>
     <t xml:space="preserve">Work: customer project</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welcome email #1: welcome + Action Plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sent from Phil on Day 0: Supered Action Plan link, kickoff booking link, first to-dos (grant HubSpot access, fill the intake form).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HubSpot email (automated on deal stage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the Supered Action Plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate the Marketing Hub Action Plan template; add the agreement, FigJam, client to-dos and access checklist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phil ↔ Architect handoff (30 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk through FigJam, customer context, products, the From→To goal, progress measures and KPIs, schedule. Architect checks the Handoff checklist section. Strategy lead moves to the Architect after this call.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting on the deal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set up progress measures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add the customer's progress measures to the project (name '&lt;Client&gt; 1.1 Visitor to Lead' etc.) with baseline, target and schedule.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.07</t>
   </si>
   <si>
@@ -1369,30 +1381,33 @@
     <t xml:space="preserve">Set Health (On track / At risk / Off track) and blockers. Escalate per the escalation path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Work: Customers row (Health)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Business Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress vs baseline, numbers trend, issues and opportunities. Architect leads; Phil optional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal delivery review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phil + Architects: at-risk customers, capacity, blockers.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Work: Portfolio</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly Business Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress vs baseline, numbers trend, issues and opportunities. Architect leads; Phil optional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal delivery review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phil + Architects: at-risk customers, capacity, blockers.</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.01</t>
   </si>
   <si>
@@ -2617,7 +2632,7 @@
     <t xml:space="preserve">HubSpot Work</t>
   </si>
   <si>
-    <t xml:space="preserve">The whole onboarding: a template project duplicated per customer, task sections by phase, board, timeline, requests log, and a portfolio for Phil.</t>
+    <t xml:space="preserve">The whole onboarding: a template project copied per customer (tasks by section, board, timeline, requests) and a Customers table where each customer's details live.</t>
   </si>
   <si>
     <t xml:space="preserve">Everything the customer sees: Action Plan, announcements, delivery and training videos, admin handbook.</t>
@@ -2635,15 +2650,237 @@
     <t xml:space="preserve">Projects object pipelines, tickets, HubSpot customer portal, Trello.</t>
   </si>
   <si>
-    <t xml:space="preserve">Template project: 'Marketing Hub Onboarding (Template)' — project fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field</t>
+    <t xml:space="preserve">Setting up a new customer (HubSpot Work has no custom project fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate 'Marketing Hub Onboarding (Template)' and name the copy exactly '&lt;Client&gt; · Marketing Hub Onboarding'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a row to Customers with Customer = that exact name, plus Company, Deal, Architect, Program length, Start date and the rest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Date Setter agent fills Project Day 0 and Program length on every task in the copy, so Due dates calculate. Without the agent, bulk-edit those two columns on all rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share the copy with the Architect (workspaces are private by default).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template project 'Marketing Hub Onboarding (Template)': Tasks table columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e.g. 4.03. First column, so 'Depends on' can be read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not started, In progress, Waiting on client, In review, Done, Won't do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phil, Architect, Ops, Client POC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HubSpot user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Person doing it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Day 0 + Due day, compressed by Program length (see rule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes/No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the customer see or do this?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly, Monthly, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What 'done' means</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anything else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase: P0 to P9 (hidden in Main table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days after Day 0, 90-day plan (hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional, for the Timeline view (hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Day 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper for the formula: same date on every row, filled per customer (hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper for the formula: 60, 75 or 90 on every row, filled per customer (hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board statuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting on client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Won't do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns = Status. Cards show Task ID, Task, Assignee, Due date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List grouped by Section (P0 → P9), sorted by Task ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start date → Due date, grouped by Section.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By Due date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignee = me, Status not Done / Won't do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client to-dos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner role = Client POC, Status not Done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date in the next 7 days, Status not Done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date before today, Status not Done / Won't do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requests table (one per customer project)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: Critical, High, Standard, Not now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: Client request, Issue found, Client idea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: New, Quoted, In progress, Done, Parked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (default 250)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio project 'Onboarding Portfolio': Customers table, one row per customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text: the customer project's exact name, '&lt;Client&gt; · Marketing Hub Onboarding'</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company</t>
   </si>
   <si>
@@ -2653,13 +2890,7 @@
     <t xml:space="preserve">CRM deal</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown: 60, 75, 90 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start date</t>
+    <t xml:space="preserve">Number: 60, 75 or 90</t>
   </si>
   <si>
     <t xml:space="preserve">Date (Day 0)</t>
@@ -2668,9 +2899,6 @@
     <t xml:space="preserve">Target end date</t>
   </si>
   <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dropdown: Professional, Enterprise</t>
   </si>
   <si>
@@ -2680,12 +2908,21 @@
     <t xml:space="preserve">Dropdown: On track, At risk, Off track</t>
   </si>
   <si>
+    <t xml:space="preserve">Current section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: P0–P9, Completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next MBR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next due task</t>
+  </si>
+  <si>
     <t xml:space="preserve">From→To goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Long text</t>
-  </si>
-  <si>
     <t xml:space="preserve">FigJam link</t>
   </si>
   <si>
@@ -2695,214 +2932,13 @@
     <t xml:space="preserve">Supered Action Plan link</t>
   </si>
   <si>
-    <t xml:space="preserve">Tasks table columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase: P0 to P9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. 4.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not started, In progress, Waiting on client, In review, Done, Won't do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phil, Architect, Ops, Client POC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Person doing it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes/No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does the customer see or do this?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days after Day 0 (90-day plan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set per customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set per customer (see compression rule)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly, Monthly, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What 'done' means</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anything else</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board statuses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting on client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Won't do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Views</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns = Status. Cards show Task ID, Task, Assignee, Due date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List grouped by Section (P0 → P9), sorted by Task ID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start date → Due date, grouped by Section.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">By Due date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignee = me, Status not Done / Won't do.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client to-dos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner role = Client POC, Status not Done.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due date in the next 7 days, Status not Done.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due date before today, Status not Done / Won't do.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requests table (one per customer project)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown: Critical, High, Standard, Not now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown: Client request, Issue found, Client idea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown: New, Quoted, In progress, Done, Parked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (default 250)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolio project: 'Onboarding Portfolio' — one row per customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text (link to the customer project)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60, 75, 90 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown P0–P9, Completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On track, At risk, Off track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next MBR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next due task</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portfolio view</t>
   </si>
   <si>
     <t xml:space="preserve">Capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Grouped by Architect, only active customers, with a count per group. Phil uses this to pick the Architect.</t>
+    <t xml:space="preserve">Report: active customers per Architect (a report, since saved views can't count). Phil uses it to pick the Architect.</t>
   </si>
   <si>
     <t xml:space="preserve">Health board</t>
@@ -2932,28 +2968,28 @@
     <t xml:space="preserve">Date Setter</t>
   </si>
   <si>
-    <t xml:space="preserve">A customer project's Start date or Program length is set or changed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill Start date and Due date on every task: date = project Start date + day. For programs shorter than 90 days, days above 10 become day × Program length ÷ 90, rounded; P9 tasks use day − 90 + Program length; P0 tasks get no date. Assign every task with Owner role 'Architect' to the project's Architect. Set Target end date = Start date + Program length.</t>
+    <t xml:space="preserve">A Customers row's Start date, Program length or Architect is set or changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the project whose name matches the row's Customer value. In its Tasks table, set Project Day 0 = the row's Start date and Program length = the row's Program length on every task, so the Due date formula calculates. Assign every task with Owner role 'Architect' to the row's Architect. Set the row's Target end date = Start date + Program length.</t>
   </si>
   <si>
     <t xml:space="preserve">Handoff Brief</t>
   </si>
   <si>
-    <t xml:space="preserve">A new row in the Portfolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read the linked deal's history, notes, meetings and emails. Write a one-page brief for the Architect in the customer project: who the customer is, the From→To goal, what they bought, the progress measures, the people involved, risks and open questions. Notify the Architect.</t>
+    <t xml:space="preserve">A new row in Customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the linked deal's history, notes, meetings and emails. Write a one-page brief for the Architect: who the customer is, the From→To goal, what they bought, the progress measures, the people involved, risks and open questions. Save it in the matching customer project and notify the Architect.</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly Update Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">Every Thursday, for each customer project in sections P2 to P8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft the Friday update in five parts: 1) work done this week and the strategic issue it moves, 2) numbers vs baseline, 3) issues found outside scope, 4) next week, 5) client to-dos. Use tasks marked Done this week, tasks due next week, and Requests logged this week. Save the draft in the project and notify the Architect, who reviews and sends it.</t>
+    <t xml:space="preserve">Every Thursday, for each Customers row whose Current section is P2 to P8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the matching project, draft the Friday update in five parts: 1) work done this week and the strategic issue it moves, 2) numbers vs baseline, 3) issues found outside scope, 4) next week, 5) client to-dos. Use tasks marked Done this week, tasks due next week, and Requests logged this week. Save the draft in the project and notify the Architect, who reviews and sends it.</t>
   </si>
   <si>
     <t xml:space="preserve">Delay Flagger</t>
@@ -2962,13 +2998,13 @@
     <t xml:space="preserve">Every weekday morning</t>
   </si>
   <si>
-    <t xml:space="preserve">Flag tasks past their Due date and tasks 'Waiting on client' for more than 3 days. If a project has 3 or more overdue tasks, set Health to At risk. Notify the Architect, and notify Phil when Health becomes At risk or Off track.</t>
+    <t xml:space="preserve">In each customer project, flag tasks past their Due date and tasks 'Waiting on client' for more than 3 days. If a project has 3 or more overdue tasks, set Health to At risk on its Customers row. Notify the Architect, and notify Phil when Health becomes At risk or Off track.</t>
   </si>
   <si>
     <t xml:space="preserve">Request Triage</t>
   </si>
   <si>
-    <t xml:space="preserve">A new row in a customer's Requests table</t>
+    <t xml:space="preserve">A new row in a customer project's Requests table</t>
   </si>
   <si>
     <t xml:space="preserve">Suggest the Urgency class and Price from the urgency rules, and set Due date from that class's turnaround. If it looks bigger than about 2 hours of work, mark it 'Quoted' and say why. Notify the Architect at once for Critical requests.</t>
@@ -2980,22 +3016,22 @@
     <t xml:space="preserve">Every day</t>
   </si>
   <si>
-    <t xml:space="preserve">For each customer project, update its Portfolio row: Current section (earliest section with open tasks), Health, Next MBR and Next due task.</t>
+    <t xml:space="preserve">For each Customers row, look at the matching project and update Current section (earliest section with open tasks), Next MBR and Next due task.</t>
   </si>
   <si>
     <t xml:space="preserve">What's Next Prep</t>
   </si>
   <si>
-    <t xml:space="preserve">35 days before a customer's Target end date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summarize results vs baseline, issues found and 'not now' requests into Option A and Option B for the next phase. Save it in the project, notify the Architect, and ask Phil to review before the call.</t>
+    <t xml:space="preserve">35 days before a Customers row's Target end date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summarize results vs baseline, issues found and 'not now' requests into Option A and Option B for the next phase. Save it in the matching project, notify the Architect, and ask Phil to review before the call.</t>
   </si>
   <si>
     <t xml:space="preserve">KPI Snapshot Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">Monthly for 6 months after a customer's Target end date</t>
+    <t xml:space="preserve">Monthly for 6 months after a Customers row's Target end date</t>
   </si>
   <si>
     <t xml:space="preserve">Draft the monthly KPI snapshot notes (3 short notes on the progress measures) for the Architect to review and send with the dashboard email.</t>
@@ -3917,207 +3953,207 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>772</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -4156,245 +4192,245 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -4430,821 +4466,825 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>867</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>869</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="A12" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>872</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>873</v>
-      </c>
-      <c r="C17" s="4"/>
+      <c r="A16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>875</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>877</v>
+        <v>661</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="C20" s="4"/>
+        <v>578</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>879</v>
+        <v>192</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>578</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="C22" s="4"/>
+        <v>883</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>884</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>886</v>
+      <c r="A25" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>888</v>
+        <v>578</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>656</v>
+        <v>193</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>573</v>
+        <v>897</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>893</v>
+        <v>191</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>895</v>
+        <v>106</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>903</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>103</v>
+        <v>904</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>872</v>
+        <v>48</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>875</v>
+        <v>901</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>875</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>906</v>
-      </c>
+      <c r="A38" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>907</v>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>908</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
+      <c r="A43" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-    </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
+      <c r="A47" s="5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3" t="s">
-        <v>918</v>
+      <c r="A52" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4" t="s">
-        <v>930</v>
-      </c>
+      <c r="A58" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>937</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C64" s="3"/>
+        <v>536</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="C62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>573</v>
+        <v>905</v>
       </c>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>531</v>
+        <v>890</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>937</v>
+        <v>905</v>
       </c>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>938</v>
+        <v>897</v>
       </c>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="C68" s="4"/>
-    </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="C69" s="4"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>875</v>
-      </c>
-      <c r="C70" s="4"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>875</v>
+        <v>945</v>
       </c>
       <c r="C71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>886</v>
+        <v>946</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>880</v>
+        <v>947</v>
       </c>
       <c r="C72" s="4"/>
     </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="C73" s="4"/>
+    </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C75" s="3"/>
-    </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>943</v>
+        <v>904</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>867</v>
+        <v>951</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>868</v>
+        <v>905</v>
       </c>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>32</v>
+        <v>625</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>870</v>
+        <v>952</v>
       </c>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>48</v>
+        <v>953</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="C79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>872</v>
+        <v>955</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>875</v>
+        <v>956</v>
       </c>
       <c r="C80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>874</v>
+        <v>957</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>875</v>
+        <v>905</v>
       </c>
       <c r="C81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>947</v>
+        <v>578</v>
       </c>
       <c r="C82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>877</v>
+        <v>959</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>948</v>
+        <v>897</v>
       </c>
       <c r="C83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>875</v>
+        <v>961</v>
       </c>
       <c r="C84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>573</v>
+        <v>961</v>
       </c>
       <c r="C85" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="4" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
     </row>
   </sheetData>
@@ -5278,201 +5318,201 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="B12" s="20" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -5507,7 +5547,7 @@
     <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5736,55 +5776,69 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="C19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>97</v>
-      </c>
+      <c r="B24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>98</v>
+      <c r="A26" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5822,7 +5876,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,84 +5975,84 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>-30</v>
@@ -6007,13 +6061,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I7" s="11" t="str">
         <f aca="false">IF(AND($D7&lt;=I$5,$E7&gt;=I$4),"■","")</f>
@@ -6078,13 +6132,13 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -6093,13 +6147,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I8" s="11" t="str">
         <f aca="false">IF(AND($D8&lt;=I$5,$E8&gt;=I$4),"■","")</f>
@@ -6164,13 +6218,13 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1</v>
@@ -6179,13 +6233,13 @@
         <v>7</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I9" s="11" t="str">
         <f aca="false">IF(AND($D9&lt;=I$5,$E9&gt;=I$4),"■","")</f>
@@ -6250,13 +6304,13 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>5</v>
@@ -6265,13 +6319,13 @@
         <v>10</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I10" s="11" t="str">
         <f aca="false">IF(AND($D10&lt;=I$5,$E10&gt;=I$4),"■","")</f>
@@ -6336,13 +6390,13 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>7</v>
@@ -6351,13 +6405,13 @@
         <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I11" s="11" t="str">
         <f aca="false">IF(AND($D11&lt;=I$5,$E11&gt;=I$4),"■","")</f>
@@ -6422,13 +6476,13 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>21</v>
@@ -6437,13 +6491,13 @@
         <v>75</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I12" s="11" t="str">
         <f aca="false">IF(AND($D12&lt;=I$5,$E12&gt;=I$4),"■","")</f>
@@ -6508,13 +6562,13 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>14</v>
@@ -6523,13 +6577,13 @@
         <v>85</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I13" s="11" t="str">
         <f aca="false">IF(AND($D13&lt;=I$5,$E13&gt;=I$4),"■","")</f>
@@ -6594,13 +6648,13 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>7</v>
@@ -6609,13 +6663,13 @@
         <v>90</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I14" s="11" t="str">
         <f aca="false">IF(AND($D14&lt;=I$5,$E14&gt;=I$4),"■","")</f>
@@ -6680,13 +6734,13 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>60</v>
@@ -6695,13 +6749,13 @@
         <v>90</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I15" s="11" t="str">
         <f aca="false">IF(AND($D15&lt;=I$5,$E15&gt;=I$4),"■","")</f>
@@ -6766,13 +6820,13 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>90</v>
@@ -6781,13 +6835,13 @@
         <v>270</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I16" s="11" t="str">
         <f aca="false">IF(AND($D16&lt;=I$5,$E16&gt;=I$4),"■","")</f>
@@ -6896,24 +6950,24 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>90</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>90</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>10</v>
@@ -7015,105 +7069,105 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>-30</v>
@@ -7128,7 +7182,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M7" s="11" t="str">
         <f aca="false">IF(AND($G7&lt;=M$5,$H7&gt;=M$4),"■","")</f>
@@ -7193,22 +7247,22 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>-25</v>
@@ -7222,10 +7276,10 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M8" s="11" t="str">
         <f aca="false">IF(AND($G8&lt;=M$5,$H8&gt;=M$4),"■","")</f>
@@ -7290,22 +7344,22 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>-25</v>
@@ -7319,10 +7373,10 @@
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M9" s="11" t="str">
         <f aca="false">IF(AND($G9&lt;=M$5,$H9&gt;=M$4),"■","")</f>
@@ -7387,22 +7441,22 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>-21</v>
@@ -7416,10 +7470,10 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M10" s="11" t="str">
         <f aca="false">IF(AND($G10&lt;=M$5,$H10&gt;=M$4),"■","")</f>
@@ -7484,22 +7538,22 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>-14</v>
@@ -7513,10 +7567,10 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M11" s="11" t="str">
         <f aca="false">IF(AND($G11&lt;=M$5,$H11&gt;=M$4),"■","")</f>
@@ -7581,22 +7635,22 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>-14</v>
@@ -7610,10 +7664,10 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M12" s="11" t="str">
         <f aca="false">IF(AND($G12&lt;=M$5,$H12&gt;=M$4),"■","")</f>
@@ -7678,22 +7732,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>-10</v>
@@ -7707,10 +7761,10 @@
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M13" s="11" t="str">
         <f aca="false">IF(AND($G13&lt;=M$5,$H13&gt;=M$4),"■","")</f>
@@ -7775,22 +7829,22 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>-5</v>
@@ -7804,10 +7858,10 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M14" s="11" t="str">
         <f aca="false">IF(AND($G14&lt;=M$5,$H14&gt;=M$4),"■","")</f>
@@ -7872,22 +7926,22 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0</v>
@@ -7901,10 +7955,10 @@
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M15" s="11" t="str">
         <f aca="false">IF(AND($G15&lt;=M$5,$H15&gt;=M$4),"■","")</f>
@@ -7967,24 +8021,24 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>0</v>
@@ -7998,10 +8052,10 @@
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M16" s="11" t="str">
         <f aca="false">IF(AND($G16&lt;=M$5,$H16&gt;=M$4),"■","")</f>
@@ -8066,22 +8120,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
@@ -8095,10 +8149,10 @@
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M17" s="11" t="str">
         <f aca="false">IF(AND($G17&lt;=M$5,$H17&gt;=M$4),"■","")</f>
@@ -8163,22 +8217,22 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>0</v>
@@ -8192,10 +8246,10 @@
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M18" s="11" t="str">
         <f aca="false">IF(AND($G18&lt;=M$5,$H18&gt;=M$4),"■","")</f>
@@ -8260,22 +8314,22 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>1</v>
@@ -8289,10 +8343,10 @@
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M19" s="11" t="str">
         <f aca="false">IF(AND($G19&lt;=M$5,$H19&gt;=M$4),"■","")</f>
@@ -8357,22 +8411,22 @@
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>1</v>
@@ -8386,10 +8440,10 @@
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="M20" s="11" t="str">
         <f aca="false">IF(AND($G20&lt;=M$5,$H20&gt;=M$4),"■","")</f>
@@ -8454,22 +8508,22 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>1</v>
@@ -8483,10 +8537,10 @@
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M21" s="11" t="str">
         <f aca="false">IF(AND($G21&lt;=M$5,$H21&gt;=M$4),"■","")</f>
@@ -8551,22 +8605,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>2</v>
@@ -8580,10 +8634,10 @@
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M22" s="11" t="str">
         <f aca="false">IF(AND($G22&lt;=M$5,$H22&gt;=M$4),"■","")</f>
@@ -8648,22 +8702,22 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>0</v>
@@ -8677,10 +8731,10 @@
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M23" s="11" t="str">
         <f aca="false">IF(AND($G23&lt;=M$5,$H23&gt;=M$4),"■","")</f>
@@ -8745,22 +8799,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>1</v>
@@ -8774,10 +8828,10 @@
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M24" s="11" t="str">
         <f aca="false">IF(AND($G24&lt;=M$5,$H24&gt;=M$4),"■","")</f>
@@ -8842,22 +8896,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="C25" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>1</v>
@@ -8871,10 +8925,10 @@
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M25" s="11" t="str">
         <f aca="false">IF(AND($G25&lt;=M$5,$H25&gt;=M$4),"■","")</f>
@@ -8939,22 +8993,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>1</v>
@@ -8968,10 +9022,10 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M26" s="11" t="str">
         <f aca="false">IF(AND($G26&lt;=M$5,$H26&gt;=M$4),"■","")</f>
@@ -9036,22 +9090,22 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>1</v>
@@ -9065,10 +9119,10 @@
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M27" s="11" t="str">
         <f aca="false">IF(AND($G27&lt;=M$5,$H27&gt;=M$4),"■","")</f>
@@ -9133,22 +9187,22 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>2</v>
@@ -9162,10 +9216,10 @@
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M28" s="11" t="str">
         <f aca="false">IF(AND($G28&lt;=M$5,$H28&gt;=M$4),"■","")</f>
@@ -9230,22 +9284,22 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>3</v>
@@ -9259,10 +9313,10 @@
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M29" s="11" t="str">
         <f aca="false">IF(AND($G29&lt;=M$5,$H29&gt;=M$4),"■","")</f>
@@ -9327,22 +9381,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>5</v>
@@ -9356,10 +9410,10 @@
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="M30" s="11" t="str">
         <f aca="false">IF(AND($G30&lt;=M$5,$H30&gt;=M$4),"■","")</f>
@@ -9424,22 +9478,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>5</v>
@@ -9453,10 +9507,10 @@
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M31" s="11" t="str">
         <f aca="false">IF(AND($G31&lt;=M$5,$H31&gt;=M$4),"■","")</f>
@@ -9521,22 +9575,22 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>295</v>
-      </c>
       <c r="C32" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>5</v>
@@ -9550,10 +9604,10 @@
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M32" s="11" t="str">
         <f aca="false">IF(AND($G32&lt;=M$5,$H32&gt;=M$4),"■","")</f>
@@ -9618,22 +9672,22 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>5</v>
@@ -9647,10 +9701,10 @@
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M33" s="11" t="str">
         <f aca="false">IF(AND($G33&lt;=M$5,$H33&gt;=M$4),"■","")</f>
@@ -9715,22 +9769,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>6</v>
@@ -9744,10 +9798,10 @@
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M34" s="11" t="str">
         <f aca="false">IF(AND($G34&lt;=M$5,$H34&gt;=M$4),"■","")</f>
@@ -9812,22 +9866,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>7</v>
@@ -9841,10 +9895,10 @@
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M35" s="11" t="str">
         <f aca="false">IF(AND($G35&lt;=M$5,$H35&gt;=M$4),"■","")</f>
@@ -9909,22 +9963,22 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>7</v>
@@ -9938,10 +9992,10 @@
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M36" s="11" t="str">
         <f aca="false">IF(AND($G36&lt;=M$5,$H36&gt;=M$4),"■","")</f>
@@ -10006,22 +10060,22 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>7</v>
@@ -10035,10 +10089,10 @@
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M37" s="11" t="str">
         <f aca="false">IF(AND($G37&lt;=M$5,$H37&gt;=M$4),"■","")</f>
@@ -10103,22 +10157,22 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>10</v>
@@ -10132,10 +10186,10 @@
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M38" s="11" t="str">
         <f aca="false">IF(AND($G38&lt;=M$5,$H38&gt;=M$4),"■","")</f>
@@ -10200,22 +10254,22 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>10</v>
@@ -10229,10 +10283,10 @@
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M39" s="11" t="str">
         <f aca="false">IF(AND($G39&lt;=M$5,$H39&gt;=M$4),"■","")</f>
@@ -10297,22 +10351,22 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>8</v>
@@ -10326,10 +10380,10 @@
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M40" s="11" t="str">
         <f aca="false">IF(AND($G40&lt;=M$5,$H40&gt;=M$4),"■","")</f>
@@ -10394,22 +10448,22 @@
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>14</v>
@@ -10423,10 +10477,10 @@
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M41" s="11" t="str">
         <f aca="false">IF(AND($G41&lt;=M$5,$H41&gt;=M$4),"■","")</f>
@@ -10491,22 +10545,22 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>14</v>
@@ -10520,10 +10574,10 @@
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M42" s="11" t="str">
         <f aca="false">IF(AND($G42&lt;=M$5,$H42&gt;=M$4),"■","")</f>
@@ -10588,22 +10642,22 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>14</v>
@@ -10617,10 +10671,10 @@
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M43" s="11" t="str">
         <f aca="false">IF(AND($G43&lt;=M$5,$H43&gt;=M$4),"■","")</f>
@@ -10685,22 +10739,22 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>18</v>
@@ -10714,10 +10768,10 @@
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M44" s="11" t="str">
         <f aca="false">IF(AND($G44&lt;=M$5,$H44&gt;=M$4),"■","")</f>
@@ -10782,22 +10836,22 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>25</v>
@@ -10811,10 +10865,10 @@
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M45" s="11" t="str">
         <f aca="false">IF(AND($G45&lt;=M$5,$H45&gt;=M$4),"■","")</f>
@@ -10879,22 +10933,22 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>28</v>
@@ -10908,10 +10962,10 @@
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M46" s="11" t="str">
         <f aca="false">IF(AND($G46&lt;=M$5,$H46&gt;=M$4),"■","")</f>
@@ -10976,22 +11030,22 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>21</v>
@@ -11005,10 +11059,10 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="M47" s="11" t="str">
         <f aca="false">IF(AND($G47&lt;=M$5,$H47&gt;=M$4),"■","")</f>
@@ -11073,22 +11127,22 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>30</v>
@@ -11102,10 +11156,10 @@
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M48" s="11" t="str">
         <f aca="false">IF(AND($G48&lt;=M$5,$H48&gt;=M$4),"■","")</f>
@@ -11170,22 +11224,22 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>35</v>
@@ -11199,10 +11253,10 @@
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="M49" s="11" t="str">
         <f aca="false">IF(AND($G49&lt;=M$5,$H49&gt;=M$4),"■","")</f>
@@ -11267,22 +11321,22 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>35</v>
@@ -11296,10 +11350,10 @@
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M50" s="11" t="str">
         <f aca="false">IF(AND($G50&lt;=M$5,$H50&gt;=M$4),"■","")</f>
@@ -11364,22 +11418,22 @@
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>30</v>
@@ -11393,10 +11447,10 @@
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M51" s="11" t="str">
         <f aca="false">IF(AND($G51&lt;=M$5,$H51&gt;=M$4),"■","")</f>
@@ -11461,22 +11515,22 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>25</v>
@@ -11490,10 +11544,10 @@
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M52" s="11" t="str">
         <f aca="false">IF(AND($G52&lt;=M$5,$H52&gt;=M$4),"■","")</f>
@@ -11558,22 +11612,22 @@
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>30</v>
@@ -11587,10 +11641,10 @@
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M53" s="11" t="str">
         <f aca="false">IF(AND($G53&lt;=M$5,$H53&gt;=M$4),"■","")</f>
@@ -11655,22 +11709,22 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>40</v>
@@ -11684,10 +11738,10 @@
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M54" s="11" t="str">
         <f aca="false">IF(AND($G54&lt;=M$5,$H54&gt;=M$4),"■","")</f>
@@ -11752,22 +11806,22 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>45</v>
@@ -11781,10 +11835,10 @@
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M55" s="11" t="str">
         <f aca="false">IF(AND($G55&lt;=M$5,$H55&gt;=M$4),"■","")</f>
@@ -11849,22 +11903,22 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>45</v>
@@ -11878,10 +11932,10 @@
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M56" s="11" t="str">
         <f aca="false">IF(AND($G56&lt;=M$5,$H56&gt;=M$4),"■","")</f>
@@ -11946,22 +12000,22 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>35</v>
@@ -11975,10 +12029,10 @@
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M57" s="11" t="str">
         <f aca="false">IF(AND($G57&lt;=M$5,$H57&gt;=M$4),"■","")</f>
@@ -12043,22 +12097,22 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>35</v>
@@ -12071,13 +12125,13 @@
         <v>75</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M58" s="11" t="str">
         <f aca="false">IF(AND($G58&lt;=M$5,$H58&gt;=M$4),"■","")</f>
@@ -12142,22 +12196,22 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>10</v>
@@ -12171,10 +12225,10 @@
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M59" s="11" t="str">
         <f aca="false">IF(AND($G59&lt;=M$5,$H59&gt;=M$4),"■","")</f>
@@ -12239,22 +12293,22 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="C60" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>14</v>
@@ -12268,10 +12322,10 @@
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M60" s="11" t="str">
         <f aca="false">IF(AND($G60&lt;=M$5,$H60&gt;=M$4),"■","")</f>
@@ -12336,22 +12390,22 @@
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>45</v>
@@ -12365,10 +12419,10 @@
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="M61" s="11" t="str">
         <f aca="false">IF(AND($G61&lt;=M$5,$H61&gt;=M$4),"■","")</f>
@@ -12433,22 +12487,22 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>60</v>
@@ -12462,10 +12516,10 @@
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M62" s="11" t="str">
         <f aca="false">IF(AND($G62&lt;=M$5,$H62&gt;=M$4),"■","")</f>
@@ -12530,22 +12584,22 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>75</v>
@@ -12559,10 +12613,10 @@
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="M63" s="11" t="str">
         <f aca="false">IF(AND($G63&lt;=M$5,$H63&gt;=M$4),"■","")</f>
@@ -12627,22 +12681,22 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>7</v>
@@ -12655,13 +12709,13 @@
         <v>90</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M64" s="11" t="str">
         <f aca="false">IF(AND($G64&lt;=M$5,$H64&gt;=M$4),"■","")</f>
@@ -12726,22 +12780,22 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>422</v>
-      </c>
       <c r="C65" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>7</v>
@@ -12754,13 +12808,13 @@
         <v>90</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M65" s="11" t="str">
         <f aca="false">IF(AND($G65&lt;=M$5,$H65&gt;=M$4),"■","")</f>
@@ -12825,22 +12879,22 @@
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>7</v>
@@ -12853,11 +12907,11 @@
         <v>90</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M66" s="11" t="str">
         <f aca="false">IF(AND($G66&lt;=M$5,$H66&gt;=M$4),"■","")</f>
@@ -12922,22 +12976,22 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>7</v>
@@ -12950,11 +13004,11 @@
         <v>90</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M67" s="11" t="str">
         <f aca="false">IF(AND($G67&lt;=M$5,$H67&gt;=M$4),"■","")</f>
@@ -13019,22 +13073,22 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>7</v>
@@ -13047,11 +13101,11 @@
         <v>90</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M68" s="11" t="str">
         <f aca="false">IF(AND($G68&lt;=M$5,$H68&gt;=M$4),"■","")</f>
@@ -13116,22 +13170,22 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>30</v>
@@ -13144,13 +13198,13 @@
         <v>60</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M69" s="11" t="str">
         <f aca="false">IF(AND($G69&lt;=M$5,$H69&gt;=M$4),"■","")</f>
@@ -13215,22 +13269,22 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>7</v>
@@ -13243,11 +13297,11 @@
         <v>90</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="M70" s="11" t="str">
         <f aca="false">IF(AND($G70&lt;=M$5,$H70&gt;=M$4),"■","")</f>
@@ -13312,22 +13366,22 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>55</v>
@@ -13341,10 +13395,10 @@
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M71" s="11" t="str">
         <f aca="false">IF(AND($G71&lt;=M$5,$H71&gt;=M$4),"■","")</f>
@@ -13409,22 +13463,22 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>60</v>
@@ -13438,10 +13492,10 @@
       </c>
       <c r="J72" s="4"/>
       <c r="K72" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M72" s="11" t="str">
         <f aca="false">IF(AND($G72&lt;=M$5,$H72&gt;=M$4),"■","")</f>
@@ -13506,22 +13560,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>451</v>
-      </c>
       <c r="C73" s="4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>62</v>
@@ -13535,10 +13589,10 @@
       </c>
       <c r="J73" s="4"/>
       <c r="K73" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M73" s="11" t="str">
         <f aca="false">IF(AND($G73&lt;=M$5,$H73&gt;=M$4),"■","")</f>
@@ -13603,22 +13657,22 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>80</v>
@@ -13632,10 +13686,10 @@
       </c>
       <c r="J74" s="4"/>
       <c r="K74" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="M74" s="11" t="str">
         <f aca="false">IF(AND($G74&lt;=M$5,$H74&gt;=M$4),"■","")</f>
@@ -13700,22 +13754,22 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>85</v>
@@ -13729,10 +13783,10 @@
       </c>
       <c r="J75" s="4"/>
       <c r="K75" s="4" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M75" s="11" t="str">
         <f aca="false">IF(AND($G75&lt;=M$5,$H75&gt;=M$4),"■","")</f>
@@ -13797,22 +13851,22 @@
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>90</v>
@@ -13825,13 +13879,13 @@
         <v>270</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M76" s="11" t="str">
         <f aca="false">IF(AND($G76&lt;=M$5,$H76&gt;=M$4),"■","")</f>
@@ -13896,22 +13950,22 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>469</v>
-      </c>
       <c r="C77" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>90</v>
@@ -13924,13 +13978,13 @@
         <v>270</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M77" s="11" t="str">
         <f aca="false">IF(AND($G77&lt;=M$5,$H77&gt;=M$4),"■","")</f>
@@ -13995,22 +14049,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>180</v>
@@ -14024,10 +14078,10 @@
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M78" s="11" t="str">
         <f aca="false">IF(AND($G78&lt;=M$5,$H78&gt;=M$4),"■","")</f>
@@ -14092,22 +14146,22 @@
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>240</v>
@@ -14121,10 +14175,10 @@
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M79" s="11" t="str">
         <f aca="false">IF(AND($G79&lt;=M$5,$H79&gt;=M$4),"■","")</f>
@@ -14189,22 +14243,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>270</v>
@@ -14218,10 +14272,10 @@
       </c>
       <c r="J80" s="4"/>
       <c r="K80" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M80" s="11" t="str">
         <f aca="false">IF(AND($G80&lt;=M$5,$H80&gt;=M$4),"■","")</f>
@@ -14286,18 +14340,18 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C83" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C84" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14354,7 +14408,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C89" s="17" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D89" s="17" t="n">
         <f aca="false">SUM(D85:D88)</f>
@@ -14422,147 +14476,147 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>499</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -14600,97 +14654,97 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -14725,62 +14779,62 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -14821,651 +14875,651 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -15505,44 +15559,44 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>32</v>
@@ -15550,19 +15604,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>32</v>
@@ -15570,19 +15624,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>32</v>
@@ -15590,19 +15644,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>32</v>
@@ -15610,19 +15664,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>32</v>
@@ -15630,19 +15684,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>32</v>
@@ -15650,19 +15704,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>32</v>
@@ -15670,19 +15724,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>32</v>
@@ -15690,19 +15744,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>32</v>
@@ -15710,39 +15764,39 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>32</v>
@@ -15750,19 +15804,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>32</v>
@@ -15770,19 +15824,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>32</v>
@@ -15790,19 +15844,19 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>32</v>
@@ -15810,19 +15864,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>32</v>
@@ -15830,19 +15884,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>32</v>
@@ -15850,19 +15904,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>32</v>
@@ -15870,19 +15924,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>32</v>
@@ -15890,19 +15944,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>32</v>
@@ -15910,19 +15964,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>32</v>
@@ -15930,19 +15984,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>32</v>
@@ -15950,19 +16004,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>32</v>
@@ -15970,19 +16024,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>32</v>
@@ -15990,19 +16044,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>32</v>
@@ -16010,19 +16064,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>32</v>
@@ -16030,19 +16084,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>32</v>
@@ -16050,19 +16104,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>32</v>
@@ -16070,19 +16124,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>32</v>
@@ -16090,19 +16144,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>32</v>
@@ -16110,19 +16164,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>32</v>
@@ -16130,19 +16184,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>32</v>
@@ -16150,19 +16204,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>32</v>
@@ -16170,19 +16224,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>32</v>
@@ -16190,19 +16244,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>32</v>
@@ -16210,19 +16264,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>32</v>
@@ -16230,19 +16284,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>32</v>
@@ -16250,19 +16304,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>32</v>
@@ -16270,19 +16324,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>32</v>
@@ -16290,19 +16344,19 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>32</v>
@@ -16310,39 +16364,39 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>32</v>
@@ -16350,19 +16404,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>32</v>
@@ -16370,19 +16424,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>32</v>
@@ -16390,19 +16444,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>32</v>

--- a/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
+++ b/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1043">
   <si>
     <t xml:space="preserve">RevGravy · Marketing Hub Onboarding Process (v2)</t>
   </si>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">60 to 90 days.</t>
   </si>
   <si>
-    <t xml:space="preserve">The plan is laid out for 90 days. Each customer project has a Program length; later due dates compress to fit 60 or 75 days.</t>
+    <t xml:space="preserve">The plan is laid out for 90 days. Each customer has a Program length on their Customers row; later due dates compress to fit 60 or 75 days.</t>
   </si>
   <si>
     <t xml:space="preserve">Hub tiers</t>
@@ -316,10 +316,10 @@
     <t xml:space="preserve">HubSpot Work limits (found in the build)</t>
   </si>
   <si>
-    <t xml:space="preserve">No custom project fields; no links between tables and projects.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer details live on the Customers table, matched to the project by its exact name. Due date uses two helper columns that the Date Setter agent fills.</t>
+    <t xml:space="preserve">No custom project fields; copies of a project don't carry agent workflows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All customers share one Customer Tasks, Requests and Updates table, each row linked to its Customers row. The template project's Tasks table is the master list the Task Generator copies from.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope limits for migration and website work (suggested)</t>
@@ -454,7 +454,7 @@
     <t xml:space="preserve">Welcome email series with the Supered Action Plan (expectations, next steps, links, agreement, to-dos).</t>
   </si>
   <si>
-    <t xml:space="preserve">Architect assigned, Phil↔Architect 1:1 done, customer project created, kickoff booked.</t>
+    <t xml:space="preserve">Architect assigned, Phil↔Architect 1:1 done, customer added in HubSpot Work with tasks created, kickoff booked.</t>
   </si>
   <si>
     <t xml:space="preserve">P2</t>
@@ -766,13 +766,13 @@
     <t xml:space="preserve">1.02</t>
   </si>
   <si>
-    <t xml:space="preserve">Create the customer project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate the 'Marketing Hub Onboarding (Template)' project and name it exactly '&lt;Client&gt; · Marketing Hub Onboarding'. Add a Customers row with that exact name plus Company, Deal, Architect, Program length and Start date. Share the project with the Architect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work: customer project + Customers row</t>
+    <t xml:space="preserve">Add the customer in HubSpot Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a Customers row: Customer, Company, Deal, Architect, Program length, Start date, tier, From→To goal, FigJam and Supered links. Check that the Task Generator created the customer's tasks (Tasks created = Yes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work: Customers table</t>
   </si>
   <si>
     <t xml:space="preserve">1.03</t>
@@ -817,10 +817,10 @@
     <t xml:space="preserve">Set up progress measures</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the customer's progress measures to the project (name '&lt;Client&gt; 1.1 Visitor to Lead' etc.) with baseline, target and schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work: customer project</t>
+    <t xml:space="preserve">Add the customer's progress measures to their Customers row (name '&lt;Client&gt; 1.1 Visitor to Lead' etc.) with baseline, target and schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work: Customers row</t>
   </si>
   <si>
     <t xml:space="preserve">1.07</t>
@@ -925,7 +925,7 @@
     <t xml:space="preserve">Data health, email health, existing assets, tracking, workflows, properties, old tool inventory. 1-page summary for kickoff.</t>
   </si>
   <si>
-    <t xml:space="preserve">Work: customer project (notes)</t>
+    <t xml:space="preserve">Work: Updates table</t>
   </si>
   <si>
     <t xml:space="preserve">2.07</t>
@@ -2632,7 +2632,7 @@
     <t xml:space="preserve">HubSpot Work</t>
   </si>
   <si>
-    <t xml:space="preserve">The whole onboarding: a template project copied per customer (tasks by section, board, timeline, requests) and a Customers table where each customer's details live.</t>
+    <t xml:space="preserve">The whole onboarding: one shared set of tables for all customers (Customers, Customer Tasks, Requests, Updates), a template task list, board, timeline and agents.</t>
   </si>
   <si>
     <t xml:space="preserve">Everything the customer sees: Action Plan, announcements, delivery and training videos, admin handbook.</t>
@@ -2650,7 +2650,7 @@
     <t xml:space="preserve">Projects object pipelines, tickets, HubSpot customer portal, Trello.</t>
   </si>
   <si>
-    <t xml:space="preserve">Setting up a new customer (HubSpot Work has no custom project fields)</t>
+    <t xml:space="preserve">Setting up a new customer (all customers share the same tables)</t>
   </si>
   <si>
     <t xml:space="preserve">Step</t>
@@ -2659,19 +2659,19 @@
     <t xml:space="preserve">What to do</t>
   </si>
   <si>
-    <t xml:space="preserve">Duplicate 'Marketing Hub Onboarding (Template)' and name the copy exactly '&lt;Client&gt; · Marketing Hub Onboarding'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a row to Customers with Customer = that exact name, plus Company, Deal, Architect, Program length, Start date and the rest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Date Setter agent fills Project Day 0 and Program length on every task in the copy, so Due dates calculate. Without the agent, bulk-edit those two columns on all rows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share the copy with the Architect (workspaces are private by default).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template project 'Marketing Hub Onboarding (Template)': Tasks table columns</t>
+    <t xml:space="preserve">Add a row to Customers: Customer, Company, Deal, Architect, Program length, Start date, tier, From→To goal, FigJam and Supered links.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Task Generator agent copies the template tasks into Customer Tasks for that customer, fills the dates, assigns the Architect and sets Tasks created = Yes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To work on one customer, filter any view by Customer. 'My tasks' shows an Architect's work across all their customers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share the workspace with Phil and the Architects (it's private by default).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task columns (template Tasks table and the shared Customer Tasks table, which adds a Customer link)</t>
   </si>
   <si>
     <t xml:space="preserve">Column</t>
@@ -2767,10 +2767,10 @@
     <t xml:space="preserve">Project Day 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Helper for the formula: same date on every row, filled per customer (hidden)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helper for the formula: 60, 75 or 90 on every row, filled per customer (hidden)</t>
+    <t xml:space="preserve">Helper for the formula: the customer's Start date, filled by the Task Generator (hidden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper for the formula: 60, 75 or 90, filled by the Task Generator (hidden)</t>
   </si>
   <si>
     <t xml:space="preserve">Board statuses</t>
@@ -2806,7 +2806,13 @@
     <t xml:space="preserve">Board</t>
   </si>
   <si>
-    <t xml:space="preserve">Columns = Status. Cards show Task ID, Task, Assignee, Due date.</t>
+    <t xml:space="preserve">Columns = Status. Cards show Customer, Task ID, Task, Assignee, Due date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List grouped by Customer, then Section, sorted by Task ID.</t>
   </si>
   <si>
     <t xml:space="preserve">By section</t>
@@ -2818,7 +2824,7 @@
     <t xml:space="preserve">Timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">Start date → Due date, grouped by Section.</t>
+    <t xml:space="preserve">Start date → Due date, grouped by Customer.</t>
   </si>
   <si>
     <t xml:space="preserve">Calendar</t>
@@ -2851,7 +2857,13 @@
     <t xml:space="preserve">Due date before today, Status not Done / Won't do.</t>
   </si>
   <si>
-    <t xml:space="preserve">Requests table (one per customer project)</t>
+    <t xml:space="preserve">Requests table (shared, each row linked to its customer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to Customers row</t>
   </si>
   <si>
     <t xml:space="preserve">Request</t>
@@ -2866,19 +2878,34 @@
     <t xml:space="preserve">Dropdown: New, Quoted, In progress, Done, Parked</t>
   </si>
   <si>
-    <t xml:space="preserve">Number (default 250)</t>
+    <t xml:space="preserve">Number, default 250</t>
   </si>
   <si>
     <t xml:space="preserve">Logged on</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio project 'Onboarding Portfolio': Customers table, one row per customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text: the customer project's exact name, '&lt;Client&gt; · Marketing Hub Onboarding'</t>
+    <t xml:space="preserve">Updates table (drafts the agents write for the Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: Handoff brief, Weekly update, What's next options, KPI snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date: week of, or month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: Draft, Reviewed, Sent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers table, one row per customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text: client name</t>
   </si>
   <si>
     <t xml:space="preserve">Company</t>
@@ -2893,7 +2920,7 @@
     <t xml:space="preserve">Number: 60, 75 or 90</t>
   </si>
   <si>
-    <t xml:space="preserve">Date (Day 0)</t>
+    <t xml:space="preserve">Date, Day 0</t>
   </si>
   <si>
     <t xml:space="preserve">Target end date</t>
@@ -2917,12 +2944,21 @@
     <t xml:space="preserve">Next MBR</t>
   </si>
   <si>
+    <t xml:space="preserve">Date, filled by the Architect when booked</t>
+  </si>
+  <si>
     <t xml:space="preserve">Next due task</t>
   </si>
   <si>
+    <t xml:space="preserve">Tasks created</t>
+  </si>
+  <si>
     <t xml:space="preserve">From→To goal</t>
   </si>
   <si>
+    <t xml:space="preserve">Long text: name, baseline, target</t>
+  </si>
+  <si>
     <t xml:space="preserve">FigJam link</t>
   </si>
   <si>
@@ -2938,7 +2974,7 @@
     <t xml:space="preserve">Capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Report: active customers per Architect (a report, since saved views can't count). Phil uses it to pick the Architect.</t>
+    <t xml:space="preserve">Report: active customers per Architect. Phil uses it to pick the Architect.</t>
   </si>
   <si>
     <t xml:space="preserve">Health board</t>
@@ -2953,7 +2989,7 @@
     <t xml:space="preserve">Target end date in the next 35 days (time for the 'what's next' call).</t>
   </si>
   <si>
-    <t xml:space="preserve">Agents (draft, fill dates or flag only; none sends anything to a customer)</t>
+    <t xml:space="preserve">Agents (draft, fill fields or flag only; none sends anything to a customer). Full prompts: hubspot-work-agent-prompts.md</t>
   </si>
   <si>
     <t xml:space="preserve">Agent</t>
@@ -2965,76 +3001,76 @@
     <t xml:space="preserve">What it does</t>
   </si>
   <si>
-    <t xml:space="preserve">Date Setter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Customers row's Start date, Program length or Architect is set or changed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find the project whose name matches the row's Customer value. In its Tasks table, set Project Day 0 = the row's Start date and Program length = the row's Program length on every task, so the Due date formula calculates. Assign every task with Owner role 'Architect' to the row's Architect. Set the row's Target end date = Start date + Program length.</t>
+    <t xml:space="preserve">Onboarding Task Generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A row in the Customers table has Start date, Program length and Architect filled, and Tasks created is not Yes. Also run when Start date, Program length or Architect changes on a row where Tasks created is Yes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copies the template tasks into Customer Tasks for a new customer, fills the dates and assigns the Architect.</t>
   </si>
   <si>
     <t xml:space="preserve">Handoff Brief</t>
   </si>
   <si>
-    <t xml:space="preserve">A new row in Customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read the linked deal's history, notes, meetings and emails. Write a one-page brief for the Architect: who the customer is, the From→To goal, what they bought, the progress measures, the people involved, risks and open questions. Save it in the matching customer project and notify the Architect.</t>
+    <t xml:space="preserve">Tasks created changes to Yes on a Customers row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Writes a one-page brief for the Architect from the deal's history.</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly Update Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">Every Thursday, for each Customers row whose Current section is P2 to P8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the matching project, draft the Friday update in five parts: 1) work done this week and the strategic issue it moves, 2) numbers vs baseline, 3) issues found outside scope, 4) next week, 5) client to-dos. Use tasks marked Done this week, tasks due next week, and Requests logged this week. Save the draft in the project and notify the Architect, who reviews and sends it.</t>
+    <t xml:space="preserve">Every Thursday at 9:00 AM (America/Phoenix).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drafts each customer's Friday update for the Architect to review and send.</t>
   </si>
   <si>
     <t xml:space="preserve">Delay Flagger</t>
   </si>
   <si>
-    <t xml:space="preserve">Every weekday morning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In each customer project, flag tasks past their Due date and tasks 'Waiting on client' for more than 3 days. If a project has 3 or more overdue tasks, set Health to At risk on its Customers row. Notify the Architect, and notify Phil when Health becomes At risk or Off track.</t>
+    <t xml:space="preserve">Every weekday at 8:00 AM (America/Phoenix).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flags overdue and stuck tasks and sets Health to At risk.</t>
   </si>
   <si>
     <t xml:space="preserve">Request Triage</t>
   </si>
   <si>
-    <t xml:space="preserve">A new row in a customer project's Requests table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggest the Urgency class and Price from the urgency rules, and set Due date from that class's turnaround. If it looks bigger than about 2 hours of work, mark it 'Quoted' and say why. Notify the Architect at once for Critical requests.</t>
+    <t xml:space="preserve">A new row is added to the Requests table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggests the urgency class, price and due date for each new request.</t>
   </si>
   <si>
     <t xml:space="preserve">Portfolio Sync</t>
   </si>
   <si>
-    <t xml:space="preserve">Every day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each Customers row, look at the matching project and update Current section (earliest section with open tasks), Next MBR and Next due task.</t>
+    <t xml:space="preserve">Every day at 6:00 AM (America/Phoenix).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keeps each customer's Current section and Next due task up to date.</t>
   </si>
   <si>
     <t xml:space="preserve">What's Next Prep</t>
   </si>
   <si>
-    <t xml:space="preserve">35 days before a Customers row's Target end date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summarize results vs baseline, issues found and 'not now' requests into Option A and Option B for the next phase. Save it in the matching project, notify the Architect, and ask Phil to review before the call.</t>
+    <t xml:space="preserve">Every day at 7:00 AM (America/Phoenix), for Customers rows whose Target end date is 35 days away or less and that don't have a 'What's next options' update yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepares Option A and Option B for the 'what's next' call.</t>
   </si>
   <si>
     <t xml:space="preserve">KPI Snapshot Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">Monthly for 6 months after a Customers row's Target end date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft the monthly KPI snapshot notes (3 short notes on the progress measures) for the Architect to review and send with the dashboard email.</t>
+    <t xml:space="preserve">The 1st of every month at 9:00 AM (America/Phoenix).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drafts the monthly KPI notes during the 6 months of free monitoring.</t>
   </si>
   <si>
     <t xml:space="preserve">Tool Fit: HubSpot Work vs Projects vs Tickets</t>
@@ -4452,7 +4488,7 @@
     <tabColor rgb="FF2E7D7A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="26"/>
@@ -4551,7 +4587,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="n">
         <v>3</v>
       </c>
@@ -4912,379 +4948,483 @@
         <v>935</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="C59" s="3"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>937</v>
-      </c>
-      <c r="B60" s="4" t="s">
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="C60" s="4"/>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="C61" s="4"/>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>939</v>
       </c>
       <c r="C62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="C64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="C63" s="4"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="C64" s="4"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>942</v>
-      </c>
       <c r="B65" s="4" t="s">
-        <v>905</v>
+        <v>944</v>
       </c>
       <c r="C65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>890</v>
+        <v>539</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>905</v>
+        <v>945</v>
       </c>
       <c r="C66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="C67" s="4"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+      <c r="C69" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="C70" s="3"/>
-    </row>
-    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>945</v>
-      </c>
-      <c r="C71" s="4"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>947</v>
-      </c>
-      <c r="C72" s="4"/>
+      <c r="C72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>464</v>
+        <v>939</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="C73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>948</v>
-      </c>
-      <c r="C73" s="4"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>888</v>
       </c>
       <c r="C74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>48</v>
+        <v>949</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>904</v>
+        <v>951</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>950</v>
+        <v>897</v>
       </c>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>951</v>
+        <v>882</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>905</v>
+        <v>952</v>
       </c>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>625</v>
+        <v>879</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>952</v>
+        <v>897</v>
       </c>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="C79" s="4"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C80" s="4"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="C81" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>578</v>
+        <v>954</v>
       </c>
       <c r="C82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>897</v>
+        <v>956</v>
       </c>
       <c r="C83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>960</v>
+        <v>464</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C85" s="4"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="C85" s="4"/>
-    </row>
-    <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+      <c r="B90" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3" t="s">
+      <c r="C90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C91" s="4"/>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C92" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="C95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C98" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>964</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>966</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>972</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>975</v>
-      </c>
-      <c r="C94" s="4" t="s">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
         <v>976</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
+      <c r="B101" s="4"/>
+      <c r="C101" s="4" t="s">
         <v>977</v>
       </c>
-      <c r="B95" s="4" t="s">
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="B102" s="4"/>
+      <c r="C102" s="4" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B103" s="4"/>
+      <c r="C103" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="C96" s="4" t="s">
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
+    <row r="106" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B106" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C106" s="8" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
+    <row r="107" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B107" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C107" s="4" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
         <v>989</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C108" s="4" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
         <v>992</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B109" s="4" t="s">
         <v>993</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C109" s="4" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
         <v>995</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B110" s="4" t="s">
         <v>996</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C110" s="4" t="s">
         <v>997</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
@@ -5318,201 +5458,201 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>862</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="B12" s="20" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -5776,7 +5916,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -8021,7 +8161,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>240</v>
       </c>

--- a/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
+++ b/marketing-hub-onboarding/Marketing_Hub_Onboarding_Process.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="1229">
   <si>
     <t xml:space="preserve">RevGravy · Marketing Hub Onboarding Process (v2)</t>
   </si>
@@ -320,13 +320,58 @@
     <t xml:space="preserve">8 agents added. They only draft, fill dates or flag; none sends anything to a customer.</t>
   </si>
   <si>
+    <t xml:space="preserve">Agent schedules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bogotá time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every scheduled agent runs on America/Bogota time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creating a customer's tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A fixed workflow, as HubSpot Work suggested.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Task Generator is a workflow that copies the 74 template tasks. The agent prompt stays as a fallback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day the deal reaches Start Payment Received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not the kickoff date. Kickoff happens on Days 5–10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update statuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft, Reviewed, Sent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An agent writes Draft; the Architect sets Reviewed, and Sent once it goes to the customer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner column, USD, reply times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each request has an Owner (default: the customer's Architect). Price is USD. High and Standard get a reply within 1 business day.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HubSpot Work limits (found in the build)</t>
   </si>
   <si>
     <t xml:space="preserve">No custom project fields; copies of a project don't carry agent workflows.</t>
   </si>
   <si>
-    <t xml:space="preserve">All customers share one Customer Tasks, Requests and Updates table, each row linked to its Customers row. The template project's Tasks table is the master list the Task Generator copies from.</t>
+    <t xml:space="preserve">All customers share the Customer Task, Request and Update tables, each row linked to its Customers row. The template project's Tasks table is the master list the Task Generator copies from.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope limits for migration and website work (suggested)</t>
@@ -659,9 +704,6 @@
     <t xml:space="preserve">Week 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Day 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Payment lands</t>
   </si>
   <si>
@@ -678,8 +720,8 @@
 • Builds the Supered Action Plan from the template and checks welcome email #1 went out.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Onboarding Task Generator creates 74 Customer Tasks with due dates, assigns the Architect's tasks, sets Target end date, Tasks created = Yes, Current section = P1 and Health = On track.
-• Handoff Brief writes a one-page draft in Updates for the Architect and Phil.</t>
+    <t xml:space="preserve">• The Task Generator workflow creates 74 Customer Task rows with due dates, assigns the Architect's tasks, sets Target end date, Tasks created = Yes, Current section = P1 and Health = On track.
+• Handoff Brief writes a one-page draft in the Update table for the Architect and Phil.</t>
   </si>
   <si>
     <t xml:space="preserve">1.01, 1.02, 1.03, 1.04</t>
@@ -705,7 +747,7 @@
 • Adds the office hours link to Supered and marks the Handoff Brief Reviewed.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Handoff Brief moves to Reviewed in Updates.
+    <t xml:space="preserve">• Handoff Brief moves to Reviewed in the Update table.
 • Portfolio Sync runs every day at 6:00 AM from now on, keeping Current section and Next due task current.</t>
   </si>
   <si>
@@ -871,7 +913,7 @@
     <t xml:space="preserve">• Edits the draft: results, issues found, 'not now' ideas, two next-phase options and the offer that fits.</t>
   </si>
   <si>
-    <t xml:space="preserve">• What's Next Prep fires 35 days before the Target end date and writes the draft in Updates.
+    <t xml:space="preserve">• What's Next Prep fires 35 days before the Target end date and writes the draft in the Update table.
 • The customer shows up in the Ending soon view.</t>
   </si>
   <si>
@@ -1535,7 +1577,7 @@
     <t xml:space="preserve">Data health, email health, existing assets, tracking, workflows, properties, old tool inventory. 1-page summary for kickoff.</t>
   </si>
   <si>
-    <t xml:space="preserve">Work: Updates table</t>
+    <t xml:space="preserve">Work: Update table</t>
   </si>
   <si>
     <t xml:space="preserve">2.07</t>
@@ -1967,7 +2009,7 @@
     <t xml:space="preserve">As they come in</t>
   </si>
   <si>
-    <t xml:space="preserve">Work: Requests table</t>
+    <t xml:space="preserve">Work: Request table</t>
   </si>
   <si>
     <t xml:space="preserve">7.04</t>
@@ -1976,7 +2018,7 @@
     <t xml:space="preserve">Log issues and 'not now' ideas</t>
   </si>
   <si>
-    <t xml:space="preserve">Out-of-scope issues and client ideas go to the Requests table as 'Not now', to sell later.</t>
+    <t xml:space="preserve">Out-of-scope issues and client ideas go to the Request table as 'Not now', to sell later.</t>
   </si>
   <si>
     <t xml:space="preserve">7.05</t>
@@ -2279,7 +2321,7 @@
     <t xml:space="preserve">Needed for a launch or deadline in the next 2 weeks.</t>
   </si>
   <si>
-    <t xml:space="preserve">Started within 2 business days; done within 5.</t>
+    <t xml:space="preserve">Reply within 1 business day; done within 5 business days.</t>
   </si>
   <si>
     <t xml:space="preserve">$250</t>
@@ -2291,7 +2333,7 @@
     <t xml:space="preserve">A small new request with no hard deadline.</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned into next week; done within 10 business days.</t>
+    <t xml:space="preserve">Reply within 1 business day; done within 10 business days.</t>
   </si>
   <si>
     <t xml:space="preserve">Not now</t>
@@ -3221,7 +3263,7 @@
     <t xml:space="preserve">Job</t>
   </si>
   <si>
-    <t xml:space="preserve">The whole onboarding: one shared set of tables for all customers (Customers, Customer Tasks, Requests, Updates), a template task list, board, timeline and agents.</t>
+    <t xml:space="preserve">The whole onboarding: one shared set of tables for all customers (Customers, Customer Task, Request, Update), a template task list, board, timeline and agents.</t>
   </si>
   <si>
     <t xml:space="preserve">Everything the customer sees: Action Plan, announcements, delivery and training videos, admin handbook.</t>
@@ -3245,7 +3287,7 @@
     <t xml:space="preserve">Add a row to Customers: Customer, Company, Deal, Architect, Program length, Start date, tier, From→To goal, FigJam and Supered links.</t>
   </si>
   <si>
-    <t xml:space="preserve">The Task Generator agent copies the template tasks into Customer Tasks for that customer, fills the dates, assigns the Architect and sets Tasks created = Yes.</t>
+    <t xml:space="preserve">The Task Generator (a workflow) copies the template tasks into Customer Task for that customer, fills the dates, assigns the Architect and sets Tasks created = Yes.</t>
   </si>
   <si>
     <t xml:space="preserve">To work on one customer, filter any view by Customer. 'My tasks' shows an Architect's work across all their customers.</t>
@@ -3254,7 +3296,7 @@
     <t xml:space="preserve">Share the workspace with Phil and the Architects (it's private by default).</t>
   </si>
   <si>
-    <t xml:space="preserve">Task columns (template Tasks table and the shared Customer Tasks table, which adds a Customer link)</t>
+    <t xml:space="preserve">Task columns (template Tasks table and the shared Customer Task table, which adds a Customer link)</t>
   </si>
   <si>
     <t xml:space="preserve">Column</t>
@@ -3419,12 +3461,15 @@
     <t xml:space="preserve">Due date before today, Status not Done / Won't do.</t>
   </si>
   <si>
-    <t xml:space="preserve">Requests table (shared, each row linked to its customer)</t>
+    <t xml:space="preserve">Request table (shared, each row linked to its customer)</t>
   </si>
   <si>
     <t xml:space="preserve">Link to Customers row</t>
   </si>
   <si>
+    <t xml:space="preserve">HubSpot user, defaults to the customer's Architect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Request</t>
   </si>
   <si>
@@ -3437,16 +3482,16 @@
     <t xml:space="preserve">Dropdown: New, Quoted, In progress, Done, Parked</t>
   </si>
   <si>
-    <t xml:space="preserve">Number, default 250</t>
+    <t xml:space="preserve">Number in USD, default 250</t>
   </si>
   <si>
     <t xml:space="preserve">Logged on</t>
   </si>
   <si>
-    <t xml:space="preserve">Updates table (drafts the agents write for the Architect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropdown: Handoff brief, Weekly update, What's next options, KPI snapshot</t>
+    <t xml:space="preserve">Update table (drafts the agents write for the Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown: Handoff brief, Weekly update, What's next options, KPI snapshot, Delay flag</t>
   </si>
   <si>
     <t xml:space="preserve">Period</t>
@@ -3458,7 +3503,7 @@
     <t xml:space="preserve">Draft</t>
   </si>
   <si>
-    <t xml:space="preserve">Dropdown: Draft, Reviewed, Sent</t>
+    <t xml:space="preserve">Dropdown: Draft (an agent wrote it), Reviewed (the Architect checked it), Sent (the Architect sent it to the customer)</t>
   </si>
   <si>
     <t xml:space="preserve">Customers table, one row per customer</t>
@@ -3479,7 +3524,7 @@
     <t xml:space="preserve">Number: 60, 75 or 90</t>
   </si>
   <si>
-    <t xml:space="preserve">Date, Day 0</t>
+    <t xml:space="preserve">Date: Day 0 = the day the deal reached Start Payment Received, not the kickoff date</t>
   </si>
   <si>
     <t xml:space="preserve">Target end date</t>
@@ -3566,7 +3611,7 @@
     <t xml:space="preserve">A row in the Customers table has Start date, Program length and Architect filled, and Tasks created is not Yes. Also run when Start date, Program length or Architect changes on a row where Tasks created is Yes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Copies the template tasks into Customer Tasks for a new customer, fills the dates and assigns the Architect.</t>
+    <t xml:space="preserve">Copies the template tasks into Customer Task for a new customer, fills the dates and assigns the Architect. Use it only if the task-seeding workflow can't be built.</t>
   </si>
   <si>
     <t xml:space="preserve">Handoff Brief</t>
@@ -3581,7 +3626,7 @@
     <t xml:space="preserve">Weekly Update Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">Every Thursday at 9:00 AM (America/Phoenix).</t>
+    <t xml:space="preserve">Every Thursday at 9:00 AM (America/Bogota).</t>
   </si>
   <si>
     <t xml:space="preserve">Drafts each customer's Friday update for the Architect to review and send.</t>
@@ -3590,7 +3635,7 @@
     <t xml:space="preserve">Delay Flagger</t>
   </si>
   <si>
-    <t xml:space="preserve">Every weekday at 8:00 AM (America/Phoenix).</t>
+    <t xml:space="preserve">Every weekday at 8:00 AM (America/Bogota).</t>
   </si>
   <si>
     <t xml:space="preserve">Flags overdue and stuck tasks and sets Health to At risk.</t>
@@ -3599,7 +3644,7 @@
     <t xml:space="preserve">Request Triage</t>
   </si>
   <si>
-    <t xml:space="preserve">A new row is added to the Requests table.</t>
+    <t xml:space="preserve">A new row is added to the Request table.</t>
   </si>
   <si>
     <t xml:space="preserve">Suggests the urgency class, price and due date for each new request.</t>
@@ -3608,7 +3653,7 @@
     <t xml:space="preserve">Portfolio Sync</t>
   </si>
   <si>
-    <t xml:space="preserve">Every day at 6:00 AM (America/Phoenix).</t>
+    <t xml:space="preserve">Every day at 6:00 AM (America/Bogota).</t>
   </si>
   <si>
     <t xml:space="preserve">Keeps each customer's Current section and Next due task up to date.</t>
@@ -3617,7 +3662,7 @@
     <t xml:space="preserve">What's Next Prep</t>
   </si>
   <si>
-    <t xml:space="preserve">Every day at 7:00 AM (America/Phoenix), for Customers rows whose Target end date is 35 days away or less and that don't have a 'What's next options' update yet.</t>
+    <t xml:space="preserve">Every day at 7:00 AM (America/Bogota), for Customers rows whose Target end date is 35 days away or less and that don't have a 'What's next options' update yet.</t>
   </si>
   <si>
     <t xml:space="preserve">Prepares Option A and Option B for the 'what's next' call.</t>
@@ -3626,7 +3671,7 @@
     <t xml:space="preserve">KPI Snapshot Drafter</t>
   </si>
   <si>
-    <t xml:space="preserve">The 1st of every month at 9:00 AM (America/Phoenix).</t>
+    <t xml:space="preserve">The 1st of every month at 9:00 AM (America/Bogota).</t>
   </si>
   <si>
     <t xml:space="preserve">Drafts the monthly KPI notes during the 6 months of free monitoring.</t>
@@ -3707,7 +3752,7 @@
     <t xml:space="preserve">Request log with urgency</t>
   </si>
   <si>
-    <t xml:space="preserve">Requests table in each project</t>
+    <t xml:space="preserve">Request table in each project</t>
   </si>
   <si>
     <t xml:space="preserve">Not its job</t>
@@ -4554,44 +4599,44 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>842</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>845</v>
+        <v>859</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>846</v>
+        <v>860</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>34</v>
@@ -4599,19 +4644,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>851</v>
+        <v>865</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>34</v>
@@ -4619,19 +4664,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>853</v>
+        <v>867</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>34</v>
@@ -4639,19 +4684,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>857</v>
+        <v>871</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
@@ -4659,19 +4704,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>859</v>
+        <v>873</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>34</v>
@@ -4679,19 +4724,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>34</v>
@@ -4699,19 +4744,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>850</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>34</v>
@@ -4719,19 +4764,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>866</v>
+        <v>880</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>34</v>
@@ -4739,19 +4784,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>868</v>
+        <v>882</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>34</v>
@@ -4759,39 +4804,39 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>870</v>
+        <v>884</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>872</v>
+        <v>886</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>34</v>
@@ -4799,19 +4844,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>876</v>
+        <v>890</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>34</v>
@@ -4819,19 +4864,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>878</v>
+        <v>892</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>34</v>
@@ -4839,19 +4884,19 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>881</v>
+        <v>895</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>882</v>
+        <v>896</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>34</v>
@@ -4859,19 +4904,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>34</v>
@@ -4879,19 +4924,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>34</v>
@@ -4899,19 +4944,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>34</v>
@@ -4919,19 +4964,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>34</v>
@@ -4939,19 +4984,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>34</v>
@@ -4959,19 +5004,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>34</v>
@@ -4979,19 +5024,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>34</v>
@@ -4999,19 +5044,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>898</v>
+        <v>912</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>34</v>
@@ -5019,19 +5064,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>34</v>
@@ -5039,19 +5084,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>34</v>
@@ -5059,19 +5104,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>904</v>
+        <v>918</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>34</v>
@@ -5079,19 +5124,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>905</v>
+        <v>919</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>34</v>
@@ -5099,19 +5144,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>34</v>
@@ -5119,19 +5164,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>909</v>
+        <v>923</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>34</v>
@@ -5139,19 +5184,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>34</v>
@@ -5159,19 +5204,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>34</v>
@@ -5179,19 +5224,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>34</v>
@@ -5199,19 +5244,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>34</v>
@@ -5219,19 +5264,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>34</v>
@@ -5239,19 +5284,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>926</v>
+        <v>940</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>34</v>
@@ -5259,19 +5304,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>927</v>
+        <v>941</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>34</v>
@@ -5279,19 +5324,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>929</v>
+        <v>943</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>34</v>
@@ -5299,19 +5344,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>34</v>
@@ -5319,19 +5364,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>34</v>
@@ -5339,19 +5384,19 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>34</v>
@@ -5359,39 +5404,39 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>34</v>
@@ -5399,19 +5444,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>34</v>
@@ -5419,19 +5464,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>34</v>
@@ -5439,19 +5484,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>949</v>
+        <v>963</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>34</v>
@@ -5493,207 +5538,207 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>953</v>
+        <v>967</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>954</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>955</v>
+        <v>969</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>957</v>
+        <v>971</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>959</v>
+        <v>973</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>960</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>961</v>
+        <v>975</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>963</v>
+        <v>977</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>965</v>
+        <v>979</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>967</v>
+        <v>981</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>968</v>
+        <v>982</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>971</v>
+        <v>985</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>972</v>
+        <v>986</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>973</v>
+        <v>987</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>975</v>
+        <v>989</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>978</v>
+        <v>992</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>979</v>
+        <v>993</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>980</v>
+        <v>994</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>981</v>
+        <v>995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>982</v>
+        <v>996</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>985</v>
+        <v>999</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>986</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>987</v>
+        <v>1001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>988</v>
+        <v>1002</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>989</v>
+        <v>1003</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>990</v>
+        <v>1004</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>991</v>
+        <v>1005</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>979</v>
+        <v>993</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>993</v>
+        <v>1007</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>995</v>
+        <v>1009</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>997</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -5732,245 +5777,245 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1002</v>
+        <v>1016</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1006</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1007</v>
+        <v>1021</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1008</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1012</v>
+        <v>1026</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1014</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1020</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1025</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1026</v>
+        <v>1040</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>1030</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>1016</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1035</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
     </row>
   </sheetData>
@@ -5992,7 +6037,7 @@
     <tabColor rgb="FF2E7D7A"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="26"/>
@@ -6006,71 +6051,71 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
-        <v>1044</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>1045</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>1050</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1051</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6079,7 +6124,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>1052</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6088,7 +6133,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>1053</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6097,7 +6142,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6106,199 +6151,199 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1059</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>846</v>
+        <v>860</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1060</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1061</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1063</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>1064</v>
+        <v>1078</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1065</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>1066</v>
+        <v>1080</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1067</v>
+        <v>1081</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1068</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1070</v>
+        <v>1084</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1071</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1072</v>
+        <v>1086</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1073</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1075</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1076</v>
+        <v>1090</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1077</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>1059</v>
+        <v>1073</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1076</v>
+        <v>1090</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1078</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1079</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>1082</v>
+        <v>1096</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>1083</v>
+        <v>1097</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1085</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1086</v>
+        <v>1100</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1087</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6306,629 +6351,638 @@
         <v>50</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1088</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>1089</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>1090</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>1091</v>
+        <v>1105</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
-        <v>1092</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>1093</v>
+        <v>1107</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
-        <v>1094</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>1095</v>
+        <v>1109</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4" t="s">
-        <v>1096</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>1097</v>
+        <v>1111</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>1098</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>1099</v>
+        <v>1113</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
-        <v>1100</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>1101</v>
+        <v>1115</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>1102</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1103</v>
+        <v>1117</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>1104</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>1105</v>
+        <v>1119</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4" t="s">
-        <v>1106</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>1107</v>
+        <v>1121</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
-        <v>1108</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>1109</v>
+        <v>1123</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>1110</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>1111</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1112</v>
+        <v>1126</v>
       </c>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1113</v>
+        <v>397</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>763</v>
+        <v>1127</v>
       </c>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>721</v>
+        <v>1128</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1114</v>
+        <v>777</v>
       </c>
       <c r="C63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>1058</v>
+        <v>735</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1115</v>
+        <v>1129</v>
       </c>
       <c r="C64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>307</v>
+        <v>1072</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1116</v>
+        <v>1130</v>
       </c>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>724</v>
+        <v>321</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1117</v>
+        <v>1131</v>
       </c>
       <c r="C66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1084</v>
+        <v>1132</v>
       </c>
       <c r="C67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>1069</v>
+        <v>1133</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="C68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>1059</v>
+        <v>1083</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1076</v>
+        <v>1098</v>
       </c>
       <c r="C69" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C73" s="4"/>
-    </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C70" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>1058</v>
+        <v>207</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>1121</v>
+        <v>1072</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="C75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1076</v>
+        <v>1137</v>
       </c>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>307</v>
+        <v>1138</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1124</v>
+        <v>1090</v>
       </c>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>1059</v>
+        <v>321</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1076</v>
+        <v>1139</v>
       </c>
       <c r="C78" s="4"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C81" s="3"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C82" s="4"/>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C79" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>1127</v>
+        <v>207</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="C83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>651</v>
+        <v>1142</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1129</v>
+        <v>1143</v>
       </c>
       <c r="C84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>34</v>
+        <v>665</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1067</v>
+        <v>1144</v>
       </c>
       <c r="C85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1130</v>
+        <v>1081</v>
       </c>
       <c r="C86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>1083</v>
+        <v>50</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1131</v>
+        <v>1145</v>
       </c>
       <c r="C87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>1132</v>
+        <v>1097</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1084</v>
+        <v>1146</v>
       </c>
       <c r="C88" s="4"/>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>810</v>
+        <v>1147</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1133</v>
+        <v>1098</v>
       </c>
       <c r="C89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>1134</v>
+        <v>824</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="C90" s="4"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="C91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="C92" s="4"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>763</v>
+        <v>1154</v>
       </c>
       <c r="C93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>1072</v>
+        <v>777</v>
       </c>
       <c r="C94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>1142</v>
+        <v>1156</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="C95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>790</v>
+        <v>1157</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1143</v>
+        <v>1090</v>
       </c>
       <c r="C96" s="4"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>1144</v>
+        <v>804</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="C97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="C98" s="4"/>
     </row>
-    <row r="100" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4" t="s">
-        <v>1149</v>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C99" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3" t="s">
+        <v>1106</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="4" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="8" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>1163</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>1167</v>
+        <v>1179</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>1169</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>1172</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>1173</v>
+        <v>1185</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>1181</v>
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -6962,201 +7016,201 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1182</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1183</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1184</v>
+        <v>1199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1185</v>
+        <v>1200</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1186</v>
+        <v>1201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1187</v>
+        <v>1202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1187</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1188</v>
+        <v>1203</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1189</v>
+        <v>1204</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1190</v>
+        <v>1205</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1191</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1192</v>
+        <v>1207</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1193</v>
+        <v>1208</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1194</v>
+        <v>1209</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1195</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1196</v>
+        <v>1211</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1197</v>
+        <v>1212</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1198</v>
+        <v>1213</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1199</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1200</v>
+        <v>1215</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1201</v>
+        <v>1216</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1204</v>
+        <v>1219</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1205</v>
+        <v>1220</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1205</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1207</v>
+        <v>1222</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1208</v>
+        <v>1223</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1209</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>1210</v>
+        <v>1225</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1211</v>
+        <v>1226</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1212</v>
+        <v>1227</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1212</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>1213</v>
+        <v>1228</v>
       </c>
       <c r="B12" s="20" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7191,7 +7245,7 @@
     <tabColor rgb="FF1F3A5F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7420,7 +7474,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -7434,55 +7488,125 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="C20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -7520,7 +7644,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,84 +7743,84 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>-30</v>
@@ -7705,13 +7829,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I7" s="11" t="str">
         <f aca="false">IF(AND($D7&lt;=I$5,$E7&gt;=I$4),"■","")</f>
@@ -7776,13 +7900,13 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -7791,13 +7915,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="I8" s="11" t="str">
         <f aca="false">IF(AND($D8&lt;=I$5,$E8&gt;=I$4),"■","")</f>
@@ -7862,13 +7986,13 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1</v>
@@ -7877,13 +8001,13 @@
         <v>7</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="I9" s="11" t="str">
         <f aca="false">IF(AND($D9&lt;=I$5,$E9&gt;=I$4),"■","")</f>
@@ -7948,13 +8072,13 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>5</v>
@@ -7963,13 +8087,13 @@
         <v>10</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="I10" s="11" t="str">
         <f aca="false">IF(AND($D10&lt;=I$5,$E10&gt;=I$4),"■","")</f>
@@ -8034,13 +8158,13 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>7</v>
@@ -8049,13 +8173,13 @@
         <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I11" s="11" t="str">
         <f aca="false">IF(AND($D11&lt;=I$5,$E11&gt;=I$4),"■","")</f>
@@ -8120,13 +8244,13 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>21</v>
@@ -8135,13 +8259,13 @@
         <v>75</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I12" s="11" t="str">
         <f aca="false">IF(AND($D12&lt;=I$5,$E12&gt;=I$4),"■","")</f>
@@ -8206,13 +8330,13 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>14</v>
@@ -8221,13 +8345,13 @@
         <v>85</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="I13" s="11" t="str">
         <f aca="false">IF(AND($D13&lt;=I$5,$E13&gt;=I$4),"■","")</f>
@@ -8292,13 +8416,13 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>7</v>
@@ -8307,13 +8431,13 @@
         <v>90</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I14" s="11" t="str">
         <f aca="false">IF(AND($D14&lt;=I$5,$E14&gt;=I$4),"■","")</f>
@@ -8378,13 +8502,13 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>60</v>
@@ -8393,13 +8517,13 @@
         <v>90</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="I15" s="11" t="str">
         <f aca="false">IF(AND($D15&lt;=I$5,$E15&gt;=I$4),"■","")</f>
@@ -8464,13 +8588,13 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>90</v>
@@ -8479,13 +8603,13 @@
         <v>270</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="I16" s="11" t="str">
         <f aca="false">IF(AND($D16&lt;=I$5,$E16&gt;=I$4),"■","")</f>
@@ -8592,21 +8716,21 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>32</v>
@@ -8618,782 +8742,782 @@
         <v>36</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="J7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="J8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="J19" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -9437,24 +9561,24 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>90</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>90</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>10</v>
@@ -9556,105 +9680,105 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>-30</v>
@@ -9669,7 +9793,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="M7" s="11" t="str">
         <f aca="false">IF(AND($G7&lt;=M$5,$H7&gt;=M$4),"■","")</f>
@@ -9734,22 +9858,22 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>-25</v>
@@ -9763,10 +9887,10 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="M8" s="11" t="str">
         <f aca="false">IF(AND($G8&lt;=M$5,$H8&gt;=M$4),"■","")</f>
@@ -9831,22 +9955,22 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>-25</v>
@@ -9860,10 +9984,10 @@
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="M9" s="11" t="str">
         <f aca="false">IF(AND($G9&lt;=M$5,$H9&gt;=M$4),"■","")</f>
@@ -9928,22 +10052,22 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>-21</v>
@@ -9957,10 +10081,10 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="M10" s="11" t="str">
         <f aca="false">IF(AND($G10&lt;=M$5,$H10&gt;=M$4),"■","")</f>
@@ -10025,22 +10149,22 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>-14</v>
@@ -10054,10 +10178,10 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="M11" s="11" t="str">
         <f aca="false">IF(AND($G11&lt;=M$5,$H11&gt;=M$4),"■","")</f>
@@ -10122,22 +10246,22 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>-14</v>
@@ -10151,10 +10275,10 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>395</v>
       </c>
       <c r="M12" s="11" t="str">
         <f aca="false">IF(AND($G12&lt;=M$5,$H12&gt;=M$4),"■","")</f>
@@ -10219,22 +10343,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>-10</v>
@@ -10248,10 +10372,10 @@
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="M13" s="11" t="str">
         <f aca="false">IF(AND($G13&lt;=M$5,$H13&gt;=M$4),"■","")</f>
@@ -10316,22 +10440,22 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>-5</v>
@@ -10345,10 +10469,10 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="M14" s="11" t="str">
         <f aca="false">IF(AND($G14&lt;=M$5,$H14&gt;=M$4),"■","")</f>
@@ -10413,22 +10537,22 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0</v>
@@ -10442,10 +10566,10 @@
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="M15" s="11" t="str">
         <f aca="false">IF(AND($G15&lt;=M$5,$H15&gt;=M$4),"■","")</f>
@@ -10510,22 +10634,22 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>0</v>
@@ -10539,10 +10663,10 @@
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="M16" s="11" t="str">
         <f aca="false">IF(AND($G16&lt;=M$5,$H16&gt;=M$4),"■","")</f>
@@ -10607,22 +10731,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
@@ -10636,10 +10760,10 @@
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="M17" s="11" t="str">
         <f aca="false">IF(AND($G17&lt;=M$5,$H17&gt;=M$4),"■","")</f>
@@ -10704,22 +10828,22 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>0</v>
@@ -10733,10 +10857,10 @@
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="M18" s="11" t="str">
         <f aca="false">IF(AND($G18&lt;=M$5,$H18&gt;=M$4),"■","")</f>
@@ -10801,22 +10925,22 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>1</v>
@@ -10830,10 +10954,10 @@
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="M19" s="11" t="str">
         <f aca="false">IF(AND($G19&lt;=M$5,$H19&gt;=M$4),"■","")</f>
@@ -10898,22 +11022,22 @@
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>1</v>
@@ -10927,10 +11051,10 @@
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="M20" s="11" t="str">
         <f aca="false">IF(AND($G20&lt;=M$5,$H20&gt;=M$4),"■","")</f>
@@ -10995,22 +11119,22 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>1</v>
@@ -11024,10 +11148,10 @@
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="M21" s="11" t="str">
         <f aca="false">IF(AND($G21&lt;=M$5,$H21&gt;=M$4),"■","")</f>
@@ -11092,22 +11216,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>2</v>
@@ -11121,10 +11245,10 @@
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="M22" s="11" t="str">
         <f aca="false">IF(AND($G22&lt;=M$5,$H22&gt;=M$4),"■","")</f>
@@ -11189,22 +11313,22 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>0</v>
@@ -11218,10 +11342,10 @@
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="M23" s="11" t="str">
         <f aca="false">IF(AND($G23&lt;=M$5,$H23&gt;=M$4),"■","")</f>
@@ -11286,22 +11410,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>1</v>
@@ -11315,10 +11439,10 @@
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="M24" s="11" t="str">
         <f aca="false">IF(AND($G24&lt;=M$5,$H24&gt;=M$4),"■","")</f>
@@ -11383,22 +11507,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>1</v>
@@ -11412,10 +11536,10 @@
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="M25" s="11" t="str">
         <f aca="false">IF(AND($G25&lt;=M$5,$H25&gt;=M$4),"■","")</f>
@@ -11480,22 +11604,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>1</v>
@@ -11509,10 +11633,10 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="M26" s="11" t="str">
         <f aca="false">IF(AND($G26&lt;=M$5,$H26&gt;=M$4),"■","")</f>
@@ -11577,22 +11701,22 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>1</v>
@@ -11606,10 +11730,10 @@
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="M27" s="11" t="str">
         <f aca="false">IF(AND($G27&lt;=M$5,$H27&gt;=M$4),"■","")</f>
@@ -11674,22 +11798,22 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>2</v>
@@ -11703,10 +11827,10 @@
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="M28" s="11" t="str">
         <f aca="false">IF(AND($G28&lt;=M$5,$H28&gt;=M$4),"■","")</f>
@@ -11771,22 +11895,22 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>3</v>
@@ -11800,10 +11924,10 @@
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="M29" s="11" t="str">
         <f aca="false">IF(AND($G29&lt;=M$5,$H29&gt;=M$4),"■","")</f>
@@ -11868,22 +11992,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>5</v>
@@ -11897,10 +12021,10 @@
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="M30" s="11" t="str">
         <f aca="false">IF(AND($G30&lt;=M$5,$H30&gt;=M$4),"■","")</f>
@@ -11965,22 +12089,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>5</v>
@@ -11994,10 +12118,10 @@
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="4" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="M31" s="11" t="str">
         <f aca="false">IF(AND($G31&lt;=M$5,$H31&gt;=M$4),"■","")</f>
@@ -12062,22 +12186,22 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>5</v>
@@ -12091,10 +12215,10 @@
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M32" s="11" t="str">
         <f aca="false">IF(AND($G32&lt;=M$5,$H32&gt;=M$4),"■","")</f>
@@ -12159,22 +12283,22 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>5</v>
@@ -12188,10 +12312,10 @@
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="M33" s="11" t="str">
         <f aca="false">IF(AND($G33&lt;=M$5,$H33&gt;=M$4),"■","")</f>
@@ -12256,22 +12380,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>6</v>
@@ -12285,10 +12409,10 @@
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="M34" s="11" t="str">
         <f aca="false">IF(AND($G34&lt;=M$5,$H34&gt;=M$4),"■","")</f>
@@ -12353,22 +12477,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>7</v>
@@ -12382,10 +12506,10 @@
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M35" s="11" t="str">
         <f aca="false">IF(AND($G35&lt;=M$5,$H35&gt;=M$4),"■","")</f>
@@ -12450,22 +12574,22 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>7</v>
@@ -12479,10 +12603,10 @@
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M36" s="11" t="str">
         <f aca="false">IF(AND($G36&lt;=M$5,$H36&gt;=M$4),"■","")</f>
@@ -12547,22 +12671,22 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>7</v>
@@ -12576,10 +12700,10 @@
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M37" s="11" t="str">
         <f aca="false">IF(AND($G37&lt;=M$5,$H37&gt;=M$4),"■","")</f>
@@ -12644,22 +12768,22 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>10</v>
@@ -12673,10 +12797,10 @@
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M38" s="11" t="str">
         <f aca="false">IF(AND($G38&lt;=M$5,$H38&gt;=M$4),"■","")</f>
@@ -12741,22 +12865,22 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>10</v>
@@ -12770,10 +12894,10 @@
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M39" s="11" t="str">
         <f aca="false">IF(AND($G39&lt;=M$5,$H39&gt;=M$4),"■","")</f>
@@ -12838,22 +12962,22 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>8</v>
@@ -12867,10 +12991,10 @@
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M40" s="11" t="str">
         <f aca="false">IF(AND($G40&lt;=M$5,$H40&gt;=M$4),"■","")</f>
@@ -12935,22 +13059,22 @@
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>14</v>
@@ -12964,10 +13088,10 @@
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M41" s="11" t="str">
         <f aca="false">IF(AND($G41&lt;=M$5,$H41&gt;=M$4),"■","")</f>
@@ -13032,22 +13156,22 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>14</v>
@@ -13061,10 +13185,10 @@
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M42" s="11" t="str">
         <f aca="false">IF(AND($G42&lt;=M$5,$H42&gt;=M$4),"■","")</f>
@@ -13129,22 +13253,22 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>14</v>
@@ -13158,10 +13282,10 @@
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M43" s="11" t="str">
         <f aca="false">IF(AND($G43&lt;=M$5,$H43&gt;=M$4),"■","")</f>
@@ -13226,22 +13350,22 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>18</v>
@@ -13255,10 +13379,10 @@
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="M44" s="11" t="str">
         <f aca="false">IF(AND($G44&lt;=M$5,$H44&gt;=M$4),"■","")</f>
@@ -13323,22 +13447,22 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>25</v>
@@ -13352,10 +13476,10 @@
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M45" s="11" t="str">
         <f aca="false">IF(AND($G45&lt;=M$5,$H45&gt;=M$4),"■","")</f>
@@ -13420,22 +13544,22 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>28</v>
@@ -13449,10 +13573,10 @@
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="M46" s="11" t="str">
         <f aca="false">IF(AND($G46&lt;=M$5,$H46&gt;=M$4),"■","")</f>
@@ -13517,22 +13641,22 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>21</v>
@@ -13546,10 +13670,10 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="M47" s="11" t="str">
         <f aca="false">IF(AND($G47&lt;=M$5,$H47&gt;=M$4),"■","")</f>
@@ -13614,22 +13738,22 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>30</v>
@@ -13643,10 +13767,10 @@
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="M48" s="11" t="str">
         <f aca="false">IF(AND($G48&lt;=M$5,$H48&gt;=M$4),"■","")</f>
@@ -13711,22 +13835,22 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>35</v>
@@ -13740,10 +13864,10 @@
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="M49" s="11" t="str">
         <f aca="false">IF(AND($G49&lt;=M$5,$H49&gt;=M$4),"■","")</f>
@@ -13808,22 +13932,22 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>546</v>
-      </c>
       <c r="C50" s="4" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>35</v>
@@ -13837,10 +13961,10 @@
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="M50" s="11" t="str">
         <f aca="false">IF(AND($G50&lt;=M$5,$H50&gt;=M$4),"■","")</f>
@@ -13905,22 +14029,22 @@
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>30</v>
@@ -13934,10 +14058,10 @@
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="M51" s="11" t="str">
         <f aca="false">IF(AND($G51&lt;=M$5,$H51&gt;=M$4),"■","")</f>
@@ -14002,22 +14126,22 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>25</v>
@@ -14031,10 +14155,10 @@
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M52" s="11" t="str">
         <f aca="false">IF(AND($G52&lt;=M$5,$H52&gt;=M$4),"■","")</f>
@@ -14099,22 +14223,22 @@
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>30</v>
@@ -14128,10 +14252,10 @@
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M53" s="11" t="str">
         <f aca="false">IF(AND($G53&lt;=M$5,$H53&gt;=M$4),"■","")</f>
@@ -14196,22 +14320,22 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>40</v>
@@ -14225,10 +14349,10 @@
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="M54" s="11" t="str">
         <f aca="false">IF(AND($G54&lt;=M$5,$H54&gt;=M$4),"■","")</f>
@@ -14293,22 +14417,22 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>45</v>
@@ -14322,10 +14446,10 @@
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="M55" s="11" t="str">
         <f aca="false">IF(AND($G55&lt;=M$5,$H55&gt;=M$4),"■","")</f>
@@ -14390,22 +14514,22 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>45</v>
@@ -14419,10 +14543,10 @@
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="M56" s="11" t="str">
         <f aca="false">IF(AND($G56&lt;=M$5,$H56&gt;=M$4),"■","")</f>
@@ -14487,22 +14611,22 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>35</v>
@@ -14516,10 +14640,10 @@
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="M57" s="11" t="str">
         <f aca="false">IF(AND($G57&lt;=M$5,$H57&gt;=M$4),"■","")</f>
@@ -14584,22 +14708,22 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>35</v>
@@ -14612,13 +14736,13 @@
         <v>75</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="M58" s="11" t="str">
         <f aca="false">IF(AND($G58&lt;=M$5,$H58&gt;=M$4),"■","")</f>
@@ -14683,22 +14807,22 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>10</v>
@@ -14712,10 +14836,10 @@
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="M59" s="11" t="str">
         <f aca="false">IF(AND($G59&lt;=M$5,$H59&gt;=M$4),"■","")</f>
@@ -14780,22 +14904,22 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>14</v>
@@ -14809,10 +14933,10 @@
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="4" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="M60" s="11" t="str">
         <f aca="false">IF(AND($G60&lt;=M$5,$H60&gt;=M$4),"■","")</f>
@@ -14877,22 +15001,22 @@
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>45</v>
@@ -14906,10 +15030,10 @@
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="4" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="M61" s="11" t="str">
         <f aca="false">IF(AND($G61&lt;=M$5,$H61&gt;=M$4),"■","")</f>
@@ -14974,22 +15098,22 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>60</v>
@@ -15003,10 +15127,10 @@
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="M62" s="11" t="str">
         <f aca="false">IF(AND($G62&lt;=M$5,$H62&gt;=M$4),"■","")</f>
@@ -15071,22 +15195,22 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>596</v>
-      </c>
       <c r="C63" s="4" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>75</v>
@@ -15100,10 +15224,10 @@
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="M63" s="11" t="str">
         <f aca="false">IF(AND($G63&lt;=M$5,$H63&gt;=M$4),"■","")</f>
@@ -15168,22 +15292,22 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>7</v>
@@ -15196,13 +15320,13 @@
         <v>90</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="M64" s="11" t="str">
         <f aca="false">IF(AND($G64&lt;=M$5,$H64&gt;=M$4),"■","")</f>
@@ -15267,22 +15391,22 @@
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>7</v>
@@ -15295,13 +15419,13 @@
         <v>90</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="M65" s="11" t="str">
         <f aca="false">IF(AND($G65&lt;=M$5,$H65&gt;=M$4),"■","")</f>
@@ -15366,22 +15490,22 @@
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>7</v>
@@ -15394,11 +15518,11 @@
         <v>90</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="M66" s="11" t="str">
         <f aca="false">IF(AND($G66&lt;=M$5,$H66&gt;=M$4),"■","")</f>
@@ -15463,22 +15587,22 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>614</v>
-      </c>
       <c r="C67" s="4" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>7</v>
@@ -15491,11 +15615,11 @@
         <v>90</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="M67" s="11" t="str">
         <f aca="false">IF(AND($G67&lt;=M$5,$H67&gt;=M$4),"■","")</f>
@@ -15560,22 +15684,22 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>7</v>
@@ -15588,11 +15712,11 @@
         <v>90</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="M68" s="11" t="str">
         <f aca="false">IF(AND($G68&lt;=M$5,$H68&gt;=M$4),"■","")</f>
@@ -15657,22 +15781,22 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>30</v>
@@ -15685,13 +15809,13 @@
         <v>60</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M69" s="11" t="str">
         <f aca="false">IF(AND($G69&lt;=M$5,$H69&gt;=M$4),"■","")</f>
@@ -15756,22 +15880,22 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>7</v>
@@ -15784,11 +15908,11 @@
         <v>90</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="M70" s="11" t="str">
         <f aca="false">IF(AND($G70&lt;=M$5,$H70&gt;=M$4),"■","")</f>
@@ -15853,22 +15977,22 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G71" s="10" t="n">
         <v>55</v>
@@ -15882,10 +16006,10 @@
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="4" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="M71" s="11" t="str">
         <f aca="false">IF(AND($G71&lt;=M$5,$H71&gt;=M$4),"■","")</f>
@@ -15950,22 +16074,22 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>60</v>
@@ -15979,10 +16103,10 @@
       </c>
       <c r="J72" s="4"/>
       <c r="K72" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M72" s="11" t="str">
         <f aca="false">IF(AND($G72&lt;=M$5,$H72&gt;=M$4),"■","")</f>
@@ -16047,22 +16171,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>62</v>
@@ -16076,10 +16200,10 @@
       </c>
       <c r="J73" s="4"/>
       <c r="K73" s="4" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="M73" s="11" t="str">
         <f aca="false">IF(AND($G73&lt;=M$5,$H73&gt;=M$4),"■","")</f>
@@ -16144,22 +16268,22 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>80</v>
@@ -16173,10 +16297,10 @@
       </c>
       <c r="J74" s="4"/>
       <c r="K74" s="4" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="M74" s="11" t="str">
         <f aca="false">IF(AND($G74&lt;=M$5,$H74&gt;=M$4),"■","")</f>
@@ -16241,22 +16365,22 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>85</v>
@@ -16270,10 +16394,10 @@
       </c>
       <c r="J75" s="4"/>
       <c r="K75" s="4" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="M75" s="11" t="str">
         <f aca="false">IF(AND($G75&lt;=M$5,$H75&gt;=M$4),"■","")</f>
@@ -16338,22 +16462,22 @@
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>90</v>
@@ -16366,13 +16490,13 @@
         <v>270</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="M76" s="11" t="str">
         <f aca="false">IF(AND($G76&lt;=M$5,$H76&gt;=M$4),"■","")</f>
@@ -16437,22 +16561,22 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>90</v>
@@ -16465,13 +16589,13 @@
         <v>270</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="M77" s="11" t="str">
         <f aca="false">IF(AND($G77&lt;=M$5,$H77&gt;=M$4),"■","")</f>
@@ -16536,22 +16660,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>180</v>
@@ -16565,10 +16689,10 @@
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="4" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M78" s="11" t="str">
         <f aca="false">IF(AND($G78&lt;=M$5,$H78&gt;=M$4),"■","")</f>
@@ -16633,22 +16757,22 @@
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>240</v>
@@ -16662,10 +16786,10 @@
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="M79" s="11" t="str">
         <f aca="false">IF(AND($G79&lt;=M$5,$H79&gt;=M$4),"■","")</f>
@@ -16730,22 +16854,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>270</v>
@@ -16759,10 +16883,10 @@
       </c>
       <c r="J80" s="4"/>
       <c r="K80" s="4" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M80" s="11" t="str">
         <f aca="false">IF(AND($G80&lt;=M$5,$H80&gt;=M$4),"■","")</f>
@@ -16827,18 +16951,18 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C83" s="5" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C84" s="3" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16895,7 +17019,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C89" s="17" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="D89" s="17" t="n">
         <f aca="false">SUM(D85:D88)</f>
@@ -16963,147 +17087,147 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>691</v>
+        <v>705</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>692</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>689</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -17141,97 +17265,97 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -17266,62 +17390,62 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>742</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>745</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>
@@ -17362,651 +17486,651 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>769</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>799</v>
+        <v>813</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>822</v>
+        <v>836</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>832</v>
+        <v>846</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>838</v>
+        <v>852</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
